--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,143 +570,143 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B27">
-        <v>18</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B28">
-        <v>73</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B29">
-        <v>159</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B30">
-        <v>273</v>
+        <v>748</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B31">
-        <v>401</v>
+        <v>953</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B32">
-        <v>538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B33">
-        <v>680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B34">
-        <v>777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B35">
-        <v>921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B36">
-        <v>1069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B37">
-        <v>1209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B38">
-        <v>1346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B39">
-        <v>1421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B40">
-        <v>1529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46080</v>
+        <v>46095</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abbcgroup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/forecast_app/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B4A0C236D0C9131E42FE31D2F8375B06A41FCE6C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CABD3BB-FEC2-49E6-B0A0-8DB69D303657}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,769 +424,769 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.010416666657</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.020833333343</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.041666666657</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.052083333343</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.072916666657</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.083333333343</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.104166666657</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.114583333343</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.135416666657</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.145833333343</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.166666666657</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.177083333343</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.197916666657</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.208333333343</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.229166666657</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.239583333343</v>
       </c>
       <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B25">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.260416666657</v>
       </c>
       <c r="B26">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.270833333343</v>
       </c>
       <c r="B27">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B28">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.291666666657</v>
       </c>
       <c r="B29">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.302083333343</v>
       </c>
       <c r="B30">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B31">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.322916666657</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.333333333343</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.354166666657</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.364583333343</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.385416666657</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.395833333343</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.416666666657</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.427083333343</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.447916666657</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.458333333343</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.479166666657</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.489583333343</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.510416666657</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.520833333343</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.541666666657</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.552083333343</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.572916666657</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.583333333343</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.604166666657</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.614583333343</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.635416666657</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.645833333343</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.666666666657</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.677083333343</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.697916666657</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.708333333343</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.729166666657</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.739583333343</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.760416666657</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.770833333343</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.791666666657</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.802083333343</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.822916666657</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.833333333343</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.854166666657</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.864583333343</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.885416666657</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.895833333343</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.916666666657</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.927083333343</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.947916666657</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.958333333343</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.979166666657</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.989583333343</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>46095</v>
+        <v>46108</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abbcgroup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/forecast_app/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B4A0C236D0C9131E42FE31D2F8375B06A41FCE6C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CABD3BB-FEC2-49E6-B0A0-8DB69D303657}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,14 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -424,769 +392,769 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46107.010416666657</v>
+        <v>46111.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46107.020833333343</v>
+        <v>46111.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46107.03125</v>
+        <v>46111.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46107.041666666657</v>
+        <v>46111.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46107.052083333343</v>
+        <v>46111.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46107.0625</v>
+        <v>46111.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46107.072916666657</v>
+        <v>46111.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46107.083333333343</v>
+        <v>46111.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46107.09375</v>
+        <v>46111.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46107.104166666657</v>
+        <v>46111.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46107.114583333343</v>
+        <v>46111.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46107.125</v>
+        <v>46111.125</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46107.135416666657</v>
+        <v>46111.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46107.145833333343</v>
+        <v>46111.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46107.15625</v>
+        <v>46111.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46107.166666666657</v>
+        <v>46111.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46107.177083333343</v>
+        <v>46111.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46107.1875</v>
+        <v>46111.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46107.197916666657</v>
+        <v>46111.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46107.208333333343</v>
+        <v>46111.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46107.21875</v>
+        <v>46111.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46107.229166666657</v>
+        <v>46111.22916666666</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46107.239583333343</v>
+        <v>46111.23958333334</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46107.25</v>
+        <v>46111.25</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46107.260416666657</v>
+        <v>46111.26041666666</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46107.270833333343</v>
+        <v>46111.27083333334</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46107.28125</v>
+        <v>46111.28125</v>
       </c>
       <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46107.291666666657</v>
+        <v>46111.29166666666</v>
       </c>
       <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46107.302083333343</v>
+        <v>46111.30208333334</v>
       </c>
       <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46107.3125</v>
+        <v>46111.3125</v>
       </c>
       <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46107.322916666657</v>
+        <v>46111.32291666666</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46107.333333333343</v>
+        <v>46111.33333333334</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46107.34375</v>
+        <v>46111.34375</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46107.354166666657</v>
+        <v>46111.35416666666</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46107.364583333343</v>
+        <v>46111.36458333334</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46107.375</v>
+        <v>46111.375</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46107.385416666657</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46107.395833333343</v>
+        <v>46111.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46107.40625</v>
+        <v>46111.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46107.416666666657</v>
+        <v>46111.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46107.427083333343</v>
+        <v>46111.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46107.4375</v>
+        <v>46111.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46107.447916666657</v>
+        <v>46111.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46107.458333333343</v>
+        <v>46111.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46107.46875</v>
+        <v>46111.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46107.479166666657</v>
+        <v>46111.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46107.489583333343</v>
+        <v>46111.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46107.5</v>
+        <v>46111.5</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46107.510416666657</v>
+        <v>46111.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46107.520833333343</v>
+        <v>46111.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46107.53125</v>
+        <v>46111.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46107.541666666657</v>
+        <v>46111.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46107.552083333343</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46107.5625</v>
+        <v>46111.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46107.572916666657</v>
+        <v>46111.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46107.583333333343</v>
+        <v>46111.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46107.59375</v>
+        <v>46111.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46107.604166666657</v>
+        <v>46111.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46107.614583333343</v>
+        <v>46111.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46107.625</v>
+        <v>46111.625</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46107.635416666657</v>
+        <v>46111.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46107.645833333343</v>
+        <v>46111.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46107.65625</v>
+        <v>46111.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46107.666666666657</v>
+        <v>46111.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46107.677083333343</v>
+        <v>46111.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46107.6875</v>
+        <v>46111.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46107.697916666657</v>
+        <v>46111.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46107.708333333343</v>
+        <v>46111.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46107.71875</v>
+        <v>46111.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46107.729166666657</v>
+        <v>46111.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46107.739583333343</v>
+        <v>46111.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46107.75</v>
+        <v>46111.75</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46107.760416666657</v>
+        <v>46111.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46107.770833333343</v>
+        <v>46111.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46107.78125</v>
+        <v>46111.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46107.791666666657</v>
+        <v>46111.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46107.802083333343</v>
+        <v>46111.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46107.8125</v>
+        <v>46111.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46107.822916666657</v>
+        <v>46111.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46107.833333333343</v>
+        <v>46111.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46107.84375</v>
+        <v>46111.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46107.854166666657</v>
+        <v>46111.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46107.864583333343</v>
+        <v>46111.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46107.875</v>
+        <v>46111.875</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46107.885416666657</v>
+        <v>46111.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46107.895833333343</v>
+        <v>46111.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46107.90625</v>
+        <v>46111.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46107.916666666657</v>
+        <v>46111.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46107.927083333343</v>
+        <v>46111.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46107.9375</v>
+        <v>46111.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46107.947916666657</v>
+        <v>46111.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46107.958333333343</v>
+        <v>46111.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46107.96875</v>
+        <v>46111.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46107.979166666657</v>
+        <v>46111.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46107.989583333343</v>
+        <v>46111.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46111.01041666666</v>
+        <v>46121</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46111.02083333334</v>
+        <v>46121.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46111.03125</v>
+        <v>46121.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46111.04166666666</v>
+        <v>46121.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46111.05208333334</v>
+        <v>46121.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46111.0625</v>
+        <v>46121.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46111.07291666666</v>
+        <v>46121.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46111.08333333334</v>
+        <v>46121.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46111.09375</v>
+        <v>46121.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46111.10416666666</v>
+        <v>46121.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46111.11458333334</v>
+        <v>46121.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46111.125</v>
+        <v>46121.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46111.13541666666</v>
+        <v>46121.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46111.14583333334</v>
+        <v>46121.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46111.15625</v>
+        <v>46121.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46111.16666666666</v>
+        <v>46121.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46111.17708333334</v>
+        <v>46121.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46111.1875</v>
+        <v>46121.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46111.19791666666</v>
+        <v>46121.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46111.20833333334</v>
+        <v>46121.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46111.21875</v>
+        <v>46121.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46111.22916666666</v>
+        <v>46121.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46111.23958333334</v>
+        <v>46121.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46111.25</v>
+        <v>46121.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -586,423 +586,423 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46111.26041666666</v>
+        <v>46121.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46111.27083333334</v>
+        <v>46121.26041666666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46111.28125</v>
+        <v>46121.27083333334</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46111.29166666666</v>
+        <v>46121.28125</v>
       </c>
       <c r="B29">
-        <v>38</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46111.30208333334</v>
+        <v>46121.29166666666</v>
       </c>
       <c r="B30">
-        <v>76</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46111.3125</v>
+        <v>46121.30208333334</v>
       </c>
       <c r="B31">
-        <v>121</v>
+        <v>410</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46111.32291666666</v>
+        <v>46121.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>581</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46111.33333333334</v>
+        <v>46121.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>722</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46111.34375</v>
+        <v>46121.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>860</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46111.35416666666</v>
+        <v>46121.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46111.36458333334</v>
+        <v>46121.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46111.375</v>
+        <v>46121.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46111.38541666666</v>
+        <v>46121.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46111.39583333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46111.40625</v>
+        <v>46121.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46111.41666666666</v>
+        <v>46121.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46111.42708333334</v>
+        <v>46121.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46111.4375</v>
+        <v>46121.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46111.44791666666</v>
+        <v>46121.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46111.45833333334</v>
+        <v>46121.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46111.46875</v>
+        <v>46121.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46111.47916666666</v>
+        <v>46121.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46111.48958333334</v>
+        <v>46121.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46111.5</v>
+        <v>46121.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46111.51041666666</v>
+        <v>46121.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>920</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46111.52083333334</v>
+        <v>46121.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>926</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46111.53125</v>
+        <v>46121.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>898</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46111.54166666666</v>
+        <v>46121.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>856</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46111.55208333334</v>
+        <v>46121.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>875</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46111.5625</v>
+        <v>46121.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>890</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46111.57291666666</v>
+        <v>46121.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>884</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46111.58333333334</v>
+        <v>46121.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>874</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46111.59375</v>
+        <v>46121.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>768</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46111.60416666666</v>
+        <v>46121.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>933</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46111.61458333334</v>
+        <v>46121.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>867</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46111.625</v>
+        <v>46121.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>771</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46111.63541666666</v>
+        <v>46121.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>729</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46111.64583333334</v>
+        <v>46121.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>722</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46111.65625</v>
+        <v>46121.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>728</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46111.66666666666</v>
+        <v>46121.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>717</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46111.67708333334</v>
+        <v>46121.66666666666</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>746</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46111.6875</v>
+        <v>46121.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>601</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46111.69791666666</v>
+        <v>46121.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>532</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46111.70833333334</v>
+        <v>46121.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>518</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46111.71875</v>
+        <v>46121.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46111.72916666666</v>
+        <v>46121.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>363</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46111.73958333334</v>
+        <v>46121.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46111.75</v>
+        <v>46121.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46111.76041666666</v>
+        <v>46121.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46111.77083333334</v>
+        <v>46121.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46111.78125</v>
+        <v>46121.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46111.79166666666</v>
+        <v>46121.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46111.80208333334</v>
+        <v>46121.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46111.8125</v>
+        <v>46121.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46111.82291666666</v>
+        <v>46121.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46111.83333333334</v>
+        <v>46121.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46111.84375</v>
+        <v>46121.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46111.85416666666</v>
+        <v>46121.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46111.86458333334</v>
+        <v>46121.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46111.875</v>
+        <v>46121.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46111.88541666666</v>
+        <v>46121.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46111.89583333334</v>
+        <v>46121.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46111.90625</v>
+        <v>46121.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46111.91666666666</v>
+        <v>46121.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46111.92708333334</v>
+        <v>46121.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46111.9375</v>
+        <v>46121.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46111.94791666666</v>
+        <v>46121.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46111.95833333334</v>
+        <v>46121.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46111.96875</v>
+        <v>46121.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46111.97916666666</v>
+        <v>46121.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46111.98958333334</v>
+        <v>46121.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46112</v>
+        <v>46121.98958333334</v>
       </c>
       <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46122.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46122.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46122.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46122.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46122.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46122.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46122.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46122.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46122.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46122.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46122.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46122.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46122.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46122.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46122.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46122.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46122.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46122.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46122.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46122.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46122.21875</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46122.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46122.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46122.25</v>
+      </c>
+      <c r="B122">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46122.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46122.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46122.28125</v>
+      </c>
+      <c r="B125">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46122.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46122.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46122.3125</v>
+      </c>
+      <c r="B128">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46122.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46122.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46122.34375</v>
+      </c>
+      <c r="B131">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46122.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46122.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46122.375</v>
+      </c>
+      <c r="B134">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46122.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46122.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46122.40625</v>
+      </c>
+      <c r="B137">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46122.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46122.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46122.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46122.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46122.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46122.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46122.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46122.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46122.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46122.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46122.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46122.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46122.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46122.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46122.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46122.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46122.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46122.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46122.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46122.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46122.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46122.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46122.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46122.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46122.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46122.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46122.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46122.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46122.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46122.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46122.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46122.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46122.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46122.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46122.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46122.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46122.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46122.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46122.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46122.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46122.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46122.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46122.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46122.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46122.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46122.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46122.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46122.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46122.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46122.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46122.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46122.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46122.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46122.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46122.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46122.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46129.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46129.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46129.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46129.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46129.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46129.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46129.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,431 +578,431 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46129.25</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B27">
-        <v>48</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46129.28125</v>
       </c>
       <c r="B28">
-        <v>102</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B29">
-        <v>199</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B30">
-        <v>293</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46129.3125</v>
       </c>
       <c r="B31">
-        <v>410</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B32">
-        <v>581</v>
+        <v>611</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B33">
-        <v>722</v>
+        <v>733</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46129.34375</v>
       </c>
       <c r="B34">
-        <v>860</v>
+        <v>876</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B35">
-        <v>1010</v>
+        <v>994</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B36">
-        <v>1151</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46129.375</v>
       </c>
       <c r="B37">
-        <v>1228</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B38">
-        <v>1374</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B39">
-        <v>1442</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46129.40625</v>
       </c>
       <c r="B40">
-        <v>1525</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B41">
-        <v>1585</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B42">
-        <v>1567</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46129.4375</v>
       </c>
       <c r="B43">
-        <v>1601</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B44">
-        <v>1621</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B45">
-        <v>1653</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46129.46875</v>
       </c>
       <c r="B46">
-        <v>1544</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B47">
-        <v>1492</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B48">
-        <v>1331</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46129.5</v>
       </c>
       <c r="B49">
-        <v>1061</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B50">
-        <v>920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B51">
-        <v>926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46129.53125</v>
       </c>
       <c r="B52">
-        <v>898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B53">
-        <v>856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B54">
-        <v>875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46129.5625</v>
       </c>
       <c r="B55">
-        <v>890</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B56">
-        <v>884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B57">
-        <v>874</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46129.59375</v>
       </c>
       <c r="B58">
-        <v>768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B59">
-        <v>933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B60">
-        <v>867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46129.625</v>
       </c>
       <c r="B61">
-        <v>771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B62">
-        <v>729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B63">
-        <v>722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46129.65625</v>
       </c>
       <c r="B64">
-        <v>728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B65">
-        <v>717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B66">
-        <v>746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46129.6875</v>
       </c>
       <c r="B67">
-        <v>601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B68">
-        <v>532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B69">
-        <v>518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46129.71875</v>
       </c>
       <c r="B70">
-        <v>447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B71">
-        <v>363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B72">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46129.75</v>
       </c>
       <c r="B73">
-        <v>246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B74">
-        <v>153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B75">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46129.78125</v>
       </c>
       <c r="B76">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B77">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46129.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46129.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46129.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46129.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46129.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46129.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,777 +1154,9 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46130</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="2">
-        <v>46122</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="2">
-        <v>46122.01041666666</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="2">
-        <v>46122.02083333334</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="2">
-        <v>46122.03125</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="2">
-        <v>46122.04166666666</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="2">
-        <v>46122.05208333334</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="2">
-        <v>46122.0625</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="2">
-        <v>46122.07291666666</v>
-      </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="2">
-        <v>46122.08333333334</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="2">
-        <v>46122.09375</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="2">
-        <v>46122.10416666666</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="2">
-        <v>46122.11458333334</v>
-      </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="2">
-        <v>46122.125</v>
-      </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="2">
-        <v>46122.13541666666</v>
-      </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="2">
-        <v>46122.14583333334</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="2">
-        <v>46122.15625</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="2">
-        <v>46122.16666666666</v>
-      </c>
-      <c r="B114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="2">
-        <v>46122.17708333334</v>
-      </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2">
-        <v>46122.1875</v>
-      </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="2">
-        <v>46122.19791666666</v>
-      </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="2">
-        <v>46122.20833333334</v>
-      </c>
-      <c r="B118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="2">
-        <v>46122.21875</v>
-      </c>
-      <c r="B119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="2">
-        <v>46122.22916666666</v>
-      </c>
-      <c r="B120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="2">
-        <v>46122.23958333334</v>
-      </c>
-      <c r="B121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>46122.25</v>
-      </c>
-      <c r="B122">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="2">
-        <v>46122.26041666666</v>
-      </c>
-      <c r="B123">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="2">
-        <v>46122.27083333334</v>
-      </c>
-      <c r="B124">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="2">
-        <v>46122.28125</v>
-      </c>
-      <c r="B125">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="2">
-        <v>46122.29166666666</v>
-      </c>
-      <c r="B126">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="2">
-        <v>46122.30208333334</v>
-      </c>
-      <c r="B127">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="2">
-        <v>46122.3125</v>
-      </c>
-      <c r="B128">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>46122.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>46122.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="2">
-        <v>46122.34375</v>
-      </c>
-      <c r="B131">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="2">
-        <v>46122.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46122.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="2">
-        <v>46122.375</v>
-      </c>
-      <c r="B134">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="2">
-        <v>46122.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="2">
-        <v>46122.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="2">
-        <v>46122.40625</v>
-      </c>
-      <c r="B137">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="2">
-        <v>46122.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="2">
-        <v>46122.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="2">
-        <v>46122.4375</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="2">
-        <v>46122.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46122.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46122.46875</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46122.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46122.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46122.5</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46122.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46122.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46122.53125</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46122.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46122.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46122.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46122.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46122.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46122.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46122.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46122.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46122.625</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46122.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46122.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46122.65625</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46122.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46122.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46122.6875</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46122.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46122.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46122.71875</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46122.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46122.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46122.75</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46122.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46122.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46122.78125</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46122.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46122.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46122.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46122.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46122.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46122.84375</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46122.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46122.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46122.875</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46122.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46122.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46122.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46122.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46122.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46122.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46122.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46122.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46122.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46122.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46122.98958333334</v>
-      </c>
-      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46129.01041666666</v>
+        <v>46132.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46129.02083333334</v>
+        <v>46132.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46129.03125</v>
+        <v>46132.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46129.04166666666</v>
+        <v>46132.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46129.05208333334</v>
+        <v>46132.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46129.0625</v>
+        <v>46132.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46129.07291666666</v>
+        <v>46132.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46129.08333333334</v>
+        <v>46132.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46129.09375</v>
+        <v>46132.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46129.10416666666</v>
+        <v>46132.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46129.11458333334</v>
+        <v>46132.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46129.125</v>
+        <v>46132.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46129.13541666666</v>
+        <v>46132.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46129.14583333334</v>
+        <v>46132.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46129.15625</v>
+        <v>46132.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46129.16666666666</v>
+        <v>46132.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46129.17708333334</v>
+        <v>46132.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46129.1875</v>
+        <v>46132.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46129.19791666666</v>
+        <v>46132.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46129.20833333334</v>
+        <v>46132.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46129.21875</v>
+        <v>46132.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46129.22916666666</v>
+        <v>46132.22916666666</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,215 +570,215 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46129.23958333334</v>
+        <v>46132.23958333334</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46129.25</v>
+        <v>46132.25</v>
       </c>
       <c r="B25">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46129.26041666666</v>
+        <v>46132.26041666666</v>
       </c>
       <c r="B26">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46129.27083333334</v>
+        <v>46132.27083333334</v>
       </c>
       <c r="B27">
-        <v>128</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46129.28125</v>
+        <v>46132.28125</v>
       </c>
       <c r="B28">
-        <v>215</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46129.29166666666</v>
+        <v>46132.29166666666</v>
       </c>
       <c r="B29">
-        <v>304</v>
+        <v>371</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46129.30208333334</v>
+        <v>46132.30208333334</v>
       </c>
       <c r="B30">
-        <v>414</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46129.3125</v>
+        <v>46132.3125</v>
       </c>
       <c r="B31">
-        <v>503</v>
+        <v>662</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46129.32291666666</v>
+        <v>46132.32291666666</v>
       </c>
       <c r="B32">
-        <v>611</v>
+        <v>792</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46129.33333333334</v>
+        <v>46132.33333333334</v>
       </c>
       <c r="B33">
-        <v>733</v>
+        <v>851</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46129.34375</v>
+        <v>46132.34375</v>
       </c>
       <c r="B34">
-        <v>876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46129.35416666666</v>
+        <v>46132.35416666666</v>
       </c>
       <c r="B35">
-        <v>994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46129.36458333334</v>
+        <v>46132.36458333334</v>
       </c>
       <c r="B36">
-        <v>1132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46129.375</v>
+        <v>46132.375</v>
       </c>
       <c r="B37">
-        <v>1253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46129.38541666666</v>
+        <v>46132.38541666666</v>
       </c>
       <c r="B38">
-        <v>1334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46129.39583333334</v>
+        <v>46132.39583333334</v>
       </c>
       <c r="B39">
-        <v>1412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46129.40625</v>
+        <v>46132.40625</v>
       </c>
       <c r="B40">
-        <v>1458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46129.41666666666</v>
+        <v>46132.41666666666</v>
       </c>
       <c r="B41">
-        <v>1518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46129.42708333334</v>
+        <v>46132.42708333334</v>
       </c>
       <c r="B42">
-        <v>1644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46129.4375</v>
+        <v>46132.4375</v>
       </c>
       <c r="B43">
-        <v>1669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46129.44791666666</v>
+        <v>46132.44791666666</v>
       </c>
       <c r="B44">
-        <v>1657</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46129.45833333334</v>
+        <v>46132.45833333334</v>
       </c>
       <c r="B45">
-        <v>1750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46129.46875</v>
+        <v>46132.46875</v>
       </c>
       <c r="B46">
-        <v>1789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46129.47916666666</v>
+        <v>46132.47916666666</v>
       </c>
       <c r="B47">
-        <v>1777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46129.48958333334</v>
+        <v>46132.48958333334</v>
       </c>
       <c r="B48">
-        <v>1775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46129.5</v>
+        <v>46132.5</v>
       </c>
       <c r="B49">
-        <v>1859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46129.51041666666</v>
+        <v>46132.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46129.52083333334</v>
+        <v>46132.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46129.53125</v>
+        <v>46132.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46129.54166666666</v>
+        <v>46132.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46129.55208333334</v>
+        <v>46132.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46129.5625</v>
+        <v>46132.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46129.57291666666</v>
+        <v>46132.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46129.58333333334</v>
+        <v>46132.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46129.59375</v>
+        <v>46132.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46129.60416666666</v>
+        <v>46132.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46129.61458333334</v>
+        <v>46132.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46129.625</v>
+        <v>46132.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46129.63541666666</v>
+        <v>46132.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46129.64583333334</v>
+        <v>46132.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46129.65625</v>
+        <v>46132.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46129.66666666666</v>
+        <v>46132.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46129.67708333334</v>
+        <v>46132.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46129.6875</v>
+        <v>46132.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46129.69791666666</v>
+        <v>46132.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46129.70833333334</v>
+        <v>46132.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46129.71875</v>
+        <v>46132.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46129.72916666666</v>
+        <v>46132.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46129.73958333334</v>
+        <v>46132.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46129.75</v>
+        <v>46132.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46129.76041666666</v>
+        <v>46132.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46129.77083333334</v>
+        <v>46132.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46129.78125</v>
+        <v>46132.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46129.79166666666</v>
+        <v>46132.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46129.80208333334</v>
+        <v>46132.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46129.8125</v>
+        <v>46132.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46129.82291666666</v>
+        <v>46132.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46129.83333333334</v>
+        <v>46132.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46129.84375</v>
+        <v>46132.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46129.85416666666</v>
+        <v>46132.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46129.86458333334</v>
+        <v>46132.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46129.875</v>
+        <v>46132.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46129.88541666666</v>
+        <v>46132.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46129.89583333334</v>
+        <v>46132.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46129.90625</v>
+        <v>46132.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46129.91666666666</v>
+        <v>46132.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46129.92708333334</v>
+        <v>46132.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46129.9375</v>
+        <v>46132.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46129.94791666666</v>
+        <v>46132.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46129.95833333334</v>
+        <v>46132.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46129.96875</v>
+        <v>46132.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46129.97916666666</v>
+        <v>46132.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46129.98958333334</v>
+        <v>46132.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46130</v>
+        <v>46133</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,151 +570,151 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B25">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B26">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B27">
-        <v>151</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B28">
-        <v>246</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B29">
-        <v>371</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B30">
-        <v>497</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B31">
-        <v>662</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B32">
-        <v>792</v>
+        <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B33">
-        <v>851</v>
+        <v>665</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>699</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>854</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>968</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46133.01041666666</v>
+        <v>46133</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46133.02083333334</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46133.03125</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46133.04166666666</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46133.05208333334</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46133.0625</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46133.07291666666</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46133.08333333334</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46133.09375</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46133.10416666666</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46133.11458333334</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46133.125</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46133.13541666666</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46133.14583333334</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46133.15625</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46133.16666666666</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46133.17708333334</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46133.1875</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46133.19791666666</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46133.20833333334</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46133.21875</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46133.22916666666</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46133.23958333334</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46133.25</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
         <v>29</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46133.26041666666</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
         <v>65</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46133.27083333334</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
         <v>126</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46133.28125</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
         <v>200</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46133.29166666666</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
         <v>283</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46133.30208333334</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
         <v>352</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46133.3125</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
         <v>425</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46133.32291666666</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
         <v>512</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46133.33333333334</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
         <v>665</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46133.34375</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
         <v>699</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46133.35416666666</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
         <v>854</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46133.36458333334</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
         <v>968</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46133.375</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
         <v>1019</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46133.38541666666</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
         <v>1092</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46133.39583333334</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
         <v>1151</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46133.40625</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
         <v>1164</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46133.41666666666</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
         <v>1063</v>
@@ -714,47 +714,47 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46133.42708333334</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46133.4375</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46133.44791666666</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46133.45833333334</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46133.46875</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46133.47916666666</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -762,255 +762,255 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46133.48958333334</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46133.5</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46133.51041666666</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46133.52083333334</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46133.53125</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46133.54166666666</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46133.55208333334</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46133.5625</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46133.57291666666</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46133.58333333334</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46133.59375</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46133.60416666666</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46133.61458333334</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46133.625</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>950</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46133.63541666666</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>939</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46133.64583333334</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>978</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46133.65625</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>935</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46133.66666666666</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>844</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46133.67708333334</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>828</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46133.6875</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>743</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46133.69791666666</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>650</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46133.70833333334</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>586</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46133.71875</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46133.72916666666</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>366</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46133.73958333334</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46133.75</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46133.76041666666</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46133.77083333334</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46133.78125</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46133.79166666666</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46133.80208333334</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46133.8125</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46133.82291666666</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46133.83333333334</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46133.84375</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46133.85416666666</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46133.86458333334</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46133.875</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46133.88541666666</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46133.89583333334</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46133.90625</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46133.91666666666</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46133.92708333334</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46133.9375</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46133.94791666666</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46133.95833333334</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46133.96875</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46133.97916666666</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46133.98958333334</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
+        <v>46133.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>46134</v>
       </c>
-      <c r="B97">
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46134.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46134.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46134.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46134.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46134.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46134.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46134.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46134.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46134.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46134.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46134.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46134.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46134.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46134.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46134.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46134.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46134.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46134.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46134.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46134.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46134.21875</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46134.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46134.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46134.25</v>
+      </c>
+      <c r="B122">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46134.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46134.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46134.28125</v>
+      </c>
+      <c r="B125">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46134.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46134.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46134.3125</v>
+      </c>
+      <c r="B128">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46134.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46134.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46134.34375</v>
+      </c>
+      <c r="B131">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46134.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46134.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46134.375</v>
+      </c>
+      <c r="B134">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46134.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46134.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46134.40625</v>
+      </c>
+      <c r="B137">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46134.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46134.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46134.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46134.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46134.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46134.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46134.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46134.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46134.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46134.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46134.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46134.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46134.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46134.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46134.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46134.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46134.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46134.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46134.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46134.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46134.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46134.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46134.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46134.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46134.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46134.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46134.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46134.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46134.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46134.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46134.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46134.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46134.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46134.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46134.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46134.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46134.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46134.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46134.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46134.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46134.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46134.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46134.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46134.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46134.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46134.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46134.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46134.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46134.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46134.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46134.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46134.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46134.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46134.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46134.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46134.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46139.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46139.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46139.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46139.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46139.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46139.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46139.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46139.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46139.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46139.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46139.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46139.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46139.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46139.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46139.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46139.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46139.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46139.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46139.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46139.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46139.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,455 +562,455 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46139.22916666666</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46139.23958333334</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46139.25</v>
       </c>
       <c r="B25">
-        <v>29</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46139.26041666666</v>
       </c>
       <c r="B26">
-        <v>65</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46139.27083333334</v>
       </c>
       <c r="B27">
-        <v>126</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46139.28125</v>
       </c>
       <c r="B28">
-        <v>200</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46139.29166666666</v>
       </c>
       <c r="B29">
-        <v>283</v>
+        <v>602</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46139.30208333334</v>
       </c>
       <c r="B30">
-        <v>352</v>
+        <v>787</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46139.3125</v>
       </c>
       <c r="B31">
-        <v>425</v>
+        <v>952</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46139.32291666666</v>
       </c>
       <c r="B32">
-        <v>512</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46139.33333333334</v>
       </c>
       <c r="B33">
-        <v>665</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46139.34375</v>
       </c>
       <c r="B34">
-        <v>699</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46139.35416666666</v>
       </c>
       <c r="B35">
-        <v>854</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46139.36458333334</v>
       </c>
       <c r="B36">
-        <v>968</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46139.375</v>
       </c>
       <c r="B37">
-        <v>1019</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46139.38541666666</v>
       </c>
       <c r="B38">
-        <v>1092</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46139.39583333334</v>
       </c>
       <c r="B39">
-        <v>1151</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46139.40625</v>
       </c>
       <c r="B40">
-        <v>1164</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46139.41666666666</v>
       </c>
       <c r="B41">
-        <v>1063</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46139.42708333334</v>
       </c>
       <c r="B42">
-        <v>1076</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46139.4375</v>
       </c>
       <c r="B43">
-        <v>1166</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46139.44791666666</v>
       </c>
       <c r="B44">
-        <v>1216</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46139.45833333334</v>
       </c>
       <c r="B45">
-        <v>1246</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46139.46875</v>
       </c>
       <c r="B46">
-        <v>1269</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46139.47916666666</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46139.48958333334</v>
       </c>
       <c r="B48">
-        <v>1262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46139.5</v>
       </c>
       <c r="B49">
-        <v>1281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46139.51041666666</v>
       </c>
       <c r="B50">
-        <v>1261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46139.52083333334</v>
       </c>
       <c r="B51">
-        <v>1297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46139.53125</v>
       </c>
       <c r="B52">
-        <v>1303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46139.54166666666</v>
       </c>
       <c r="B53">
-        <v>1228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46139.55208333334</v>
       </c>
       <c r="B54">
-        <v>1183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46139.5625</v>
       </c>
       <c r="B55">
-        <v>1134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46139.57291666666</v>
       </c>
       <c r="B56">
-        <v>1138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46139.58333333334</v>
       </c>
       <c r="B57">
-        <v>1115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46139.59375</v>
       </c>
       <c r="B58">
-        <v>1104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46139.60416666666</v>
       </c>
       <c r="B59">
-        <v>1130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46139.61458333334</v>
       </c>
       <c r="B60">
-        <v>1070</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46139.625</v>
       </c>
       <c r="B61">
-        <v>950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46139.63541666666</v>
       </c>
       <c r="B62">
-        <v>939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46139.64583333334</v>
       </c>
       <c r="B63">
-        <v>978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46139.65625</v>
       </c>
       <c r="B64">
-        <v>935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46139.66666666666</v>
       </c>
       <c r="B65">
-        <v>844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46139.67708333334</v>
       </c>
       <c r="B66">
-        <v>828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46139.6875</v>
       </c>
       <c r="B67">
-        <v>743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46139.69791666666</v>
       </c>
       <c r="B68">
-        <v>650</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46139.70833333334</v>
       </c>
       <c r="B69">
-        <v>586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46139.71875</v>
       </c>
       <c r="B70">
-        <v>492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46139.72916666666</v>
       </c>
       <c r="B71">
-        <v>366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46139.73958333334</v>
       </c>
       <c r="B72">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46139.75</v>
       </c>
       <c r="B73">
-        <v>238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46139.76041666666</v>
       </c>
       <c r="B74">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46139.77083333334</v>
       </c>
       <c r="B75">
-        <v>101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46139.78125</v>
       </c>
       <c r="B76">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46139.79166666666</v>
       </c>
       <c r="B77">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46139.80208333334</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46139.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46139.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46139.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46139.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46139.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46139.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46139.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46139.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46139.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46139.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46139.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46139.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46139.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46139.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46139.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46139.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46139.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46139.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,777 +1154,9 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46140</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="2">
-        <v>46134</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="2">
-        <v>46134.01041666666</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="2">
-        <v>46134.02083333334</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="2">
-        <v>46134.03125</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="2">
-        <v>46134.04166666666</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="2">
-        <v>46134.05208333334</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="2">
-        <v>46134.0625</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="2">
-        <v>46134.07291666666</v>
-      </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="2">
-        <v>46134.08333333334</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="2">
-        <v>46134.09375</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="2">
-        <v>46134.10416666666</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="2">
-        <v>46134.11458333334</v>
-      </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="2">
-        <v>46134.125</v>
-      </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="2">
-        <v>46134.13541666666</v>
-      </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="2">
-        <v>46134.14583333334</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="2">
-        <v>46134.15625</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="2">
-        <v>46134.16666666666</v>
-      </c>
-      <c r="B114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="2">
-        <v>46134.17708333334</v>
-      </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2">
-        <v>46134.1875</v>
-      </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="2">
-        <v>46134.19791666666</v>
-      </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="2">
-        <v>46134.20833333334</v>
-      </c>
-      <c r="B118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="2">
-        <v>46134.21875</v>
-      </c>
-      <c r="B119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="2">
-        <v>46134.22916666666</v>
-      </c>
-      <c r="B120">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="2">
-        <v>46134.23958333334</v>
-      </c>
-      <c r="B121">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>46134.25</v>
-      </c>
-      <c r="B122">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="2">
-        <v>46134.26041666666</v>
-      </c>
-      <c r="B123">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="2">
-        <v>46134.27083333334</v>
-      </c>
-      <c r="B124">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="2">
-        <v>46134.28125</v>
-      </c>
-      <c r="B125">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="2">
-        <v>46134.29166666666</v>
-      </c>
-      <c r="B126">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="2">
-        <v>46134.30208333334</v>
-      </c>
-      <c r="B127">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="2">
-        <v>46134.3125</v>
-      </c>
-      <c r="B128">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>46134.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>46134.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="2">
-        <v>46134.34375</v>
-      </c>
-      <c r="B131">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="2">
-        <v>46134.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46134.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="2">
-        <v>46134.375</v>
-      </c>
-      <c r="B134">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="2">
-        <v>46134.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="2">
-        <v>46134.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="2">
-        <v>46134.40625</v>
-      </c>
-      <c r="B137">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="2">
-        <v>46134.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>1435</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="2">
-        <v>46134.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="2">
-        <v>46134.4375</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="2">
-        <v>46134.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46134.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46134.46875</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46134.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46134.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46134.5</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46134.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46134.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46134.53125</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46134.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46134.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46134.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46134.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46134.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46134.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46134.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46134.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46134.625</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46134.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46134.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46134.65625</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46134.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46134.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46134.6875</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46134.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46134.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46134.71875</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46134.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46134.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46134.75</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46134.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46134.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46134.78125</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46134.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46134.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46134.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46134.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46134.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46134.84375</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46134.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46134.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46134.875</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46134.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46134.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46134.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46134.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46134.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46134.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46134.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46134.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46134.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46134.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46134.98958333334</v>
-      </c>
-      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46139.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46139.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46139.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46139.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46139.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46139.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46139.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46139.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46139.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46139.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46139.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46139.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46139.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46139.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46139.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46139.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46139.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46139.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46139.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46139.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46139.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,207 +562,207 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46139.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46139.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B24">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46139.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B25">
-        <v>76</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46139.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B26">
-        <v>150</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46139.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B27">
-        <v>263</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46139.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B28">
-        <v>406</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46139.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B29">
-        <v>602</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46139.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B30">
-        <v>787</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46139.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B31">
-        <v>952</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46139.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B32">
-        <v>1137</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46139.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B33">
-        <v>1297</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46139.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B34">
-        <v>1442</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46139.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B35">
-        <v>1566</v>
+        <v>515</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46139.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B36">
-        <v>1667</v>
+        <v>568</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46139.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B37">
-        <v>1812</v>
+        <v>641</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46139.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B38">
-        <v>1898</v>
+        <v>732</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46139.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B39">
-        <v>2062</v>
+        <v>801</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46139.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B40">
-        <v>2154</v>
+        <v>818</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46139.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B41">
-        <v>2170</v>
+        <v>789</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46139.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B42">
-        <v>2267</v>
+        <v>858</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46139.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B43">
-        <v>2248</v>
+        <v>841</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46139.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B44">
-        <v>2279</v>
+        <v>853</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46139.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B45">
-        <v>2310</v>
+        <v>950</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46139.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B46">
-        <v>2256</v>
+        <v>987</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46139.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B47">
-        <v>1959</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46139.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46139.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46139.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46139.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46139.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46139.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46139.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46139.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46139.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46139.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46139.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46139.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46139.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46139.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46139.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46139.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46139.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46139.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46139.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46139.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46139.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46139.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46139.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46139.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46139.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46139.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46139.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46139.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46139.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46139.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46139.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46139.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46139.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46139.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46139.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46139.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46139.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46139.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46139.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46139.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46139.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46139.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46139.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46139.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46139.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46139.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46139.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46139.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46139.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46142.01041666666</v>
+        <v>46146.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46142.02083333334</v>
+        <v>46146.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46142.03125</v>
+        <v>46146.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46142.04166666666</v>
+        <v>46146.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46142.05208333334</v>
+        <v>46146.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46142.0625</v>
+        <v>46146.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46142.07291666666</v>
+        <v>46146.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46142.08333333334</v>
+        <v>46146.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46142.09375</v>
+        <v>46146.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46142.10416666666</v>
+        <v>46146.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46142.11458333334</v>
+        <v>46146.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46142.125</v>
+        <v>46146.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46142.13541666666</v>
+        <v>46146.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46142.14583333334</v>
+        <v>46146.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46142.15625</v>
+        <v>46146.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46142.16666666666</v>
+        <v>46146.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46142.17708333334</v>
+        <v>46146.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46142.1875</v>
+        <v>46146.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46142.19791666666</v>
+        <v>46146.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46142.20833333334</v>
+        <v>46146.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46142.21875</v>
+        <v>46146.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,207 +562,207 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46142.22916666666</v>
+        <v>46146.22916666666</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46142.23958333334</v>
+        <v>46146.23958333334</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46142.25</v>
+        <v>46146.25</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46142.26041666666</v>
+        <v>46146.26041666666</v>
       </c>
       <c r="B26">
-        <v>38</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46142.27083333334</v>
+        <v>46146.27083333334</v>
       </c>
       <c r="B27">
-        <v>67</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46142.28125</v>
+        <v>46146.28125</v>
       </c>
       <c r="B28">
-        <v>97</v>
+        <v>459</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46142.29166666666</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="B29">
-        <v>136</v>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46142.30208333334</v>
+        <v>46146.30208333334</v>
       </c>
       <c r="B30">
-        <v>178</v>
+        <v>824</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46142.3125</v>
+        <v>46146.3125</v>
       </c>
       <c r="B31">
-        <v>234</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46142.32291666666</v>
+        <v>46146.32291666666</v>
       </c>
       <c r="B32">
-        <v>303</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46142.33333333334</v>
+        <v>46146.33333333334</v>
       </c>
       <c r="B33">
-        <v>369</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46142.34375</v>
+        <v>46146.34375</v>
       </c>
       <c r="B34">
-        <v>430</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46142.35416666666</v>
+        <v>46146.35416666666</v>
       </c>
       <c r="B35">
-        <v>515</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46142.36458333334</v>
+        <v>46146.36458333334</v>
       </c>
       <c r="B36">
-        <v>568</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46142.375</v>
+        <v>46146.375</v>
       </c>
       <c r="B37">
-        <v>641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46142.38541666666</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="B38">
-        <v>732</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46142.39583333334</v>
+        <v>46146.39583333334</v>
       </c>
       <c r="B39">
-        <v>801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46142.40625</v>
+        <v>46146.40625</v>
       </c>
       <c r="B40">
-        <v>818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46142.41666666666</v>
+        <v>46146.41666666666</v>
       </c>
       <c r="B41">
-        <v>789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46142.42708333334</v>
+        <v>46146.42708333334</v>
       </c>
       <c r="B42">
-        <v>858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46142.4375</v>
+        <v>46146.4375</v>
       </c>
       <c r="B43">
-        <v>841</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46142.44791666666</v>
+        <v>46146.44791666666</v>
       </c>
       <c r="B44">
-        <v>853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46142.45833333334</v>
+        <v>46146.45833333334</v>
       </c>
       <c r="B45">
-        <v>950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46142.46875</v>
+        <v>46146.46875</v>
       </c>
       <c r="B46">
-        <v>987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46142.47916666666</v>
+        <v>46146.47916666666</v>
       </c>
       <c r="B47">
-        <v>1056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46142.48958333334</v>
+        <v>46146.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46142.5</v>
+        <v>46146.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46142.51041666666</v>
+        <v>46146.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46142.52083333334</v>
+        <v>46146.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46142.53125</v>
+        <v>46146.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46142.54166666666</v>
+        <v>46146.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46142.55208333334</v>
+        <v>46146.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46142.5625</v>
+        <v>46146.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46142.57291666666</v>
+        <v>46146.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46142.58333333334</v>
+        <v>46146.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46142.59375</v>
+        <v>46146.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46142.60416666666</v>
+        <v>46146.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46142.61458333334</v>
+        <v>46146.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46142.625</v>
+        <v>46146.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46142.63541666666</v>
+        <v>46146.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46142.64583333334</v>
+        <v>46146.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46142.65625</v>
+        <v>46146.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46142.66666666666</v>
+        <v>46146.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46142.67708333334</v>
+        <v>46146.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46142.6875</v>
+        <v>46146.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46142.69791666666</v>
+        <v>46146.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46142.70833333334</v>
+        <v>46146.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46142.71875</v>
+        <v>46146.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46142.72916666666</v>
+        <v>46146.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46142.73958333334</v>
+        <v>46146.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46142.75</v>
+        <v>46146.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46142.76041666666</v>
+        <v>46146.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46142.77083333334</v>
+        <v>46146.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46142.78125</v>
+        <v>46146.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46142.79166666666</v>
+        <v>46146.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46142.80208333334</v>
+        <v>46146.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46142.8125</v>
+        <v>46146.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46142.82291666666</v>
+        <v>46146.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46142.83333333334</v>
+        <v>46146.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46142.84375</v>
+        <v>46146.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46142.85416666666</v>
+        <v>46146.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46142.86458333334</v>
+        <v>46146.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46142.875</v>
+        <v>46146.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46142.88541666666</v>
+        <v>46146.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46142.89583333334</v>
+        <v>46146.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46142.90625</v>
+        <v>46146.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46142.91666666666</v>
+        <v>46146.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46142.92708333334</v>
+        <v>46146.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46142.9375</v>
+        <v>46146.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46142.94791666666</v>
+        <v>46146.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46142.95833333334</v>
+        <v>46146.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46142.96875</v>
+        <v>46146.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46142.97916666666</v>
+        <v>46146.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46142.98958333334</v>
+        <v>46146.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46146.01041666666</v>
+        <v>46148.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46146.02083333334</v>
+        <v>46148.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46146.03125</v>
+        <v>46148.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46146.04166666666</v>
+        <v>46148.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46146.05208333334</v>
+        <v>46148.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46146.0625</v>
+        <v>46148.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46146.07291666666</v>
+        <v>46148.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46146.08333333334</v>
+        <v>46148.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46146.09375</v>
+        <v>46148.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46146.10416666666</v>
+        <v>46148.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46146.11458333334</v>
+        <v>46148.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46146.125</v>
+        <v>46148.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46146.13541666666</v>
+        <v>46148.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46146.14583333334</v>
+        <v>46148.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46146.15625</v>
+        <v>46148.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46146.16666666666</v>
+        <v>46148.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46146.17708333334</v>
+        <v>46148.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46146.1875</v>
+        <v>46148.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46146.19791666666</v>
+        <v>46148.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46146.20833333334</v>
+        <v>46148.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46146.21875</v>
+        <v>46148.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,119 +562,119 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46146.22916666666</v>
+        <v>46148.22916666666</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46146.23958333334</v>
+        <v>46148.23958333334</v>
       </c>
       <c r="B24">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46146.25</v>
+        <v>46148.25</v>
       </c>
       <c r="B25">
-        <v>93</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46146.26041666666</v>
+        <v>46148.26041666666</v>
       </c>
       <c r="B26">
-        <v>188</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46146.27083333334</v>
+        <v>46148.27083333334</v>
       </c>
       <c r="B27">
-        <v>312</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46146.28125</v>
+        <v>46148.28125</v>
       </c>
       <c r="B28">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46146.29166666666</v>
+        <v>46148.29166666666</v>
       </c>
       <c r="B29">
-        <v>595</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46146.30208333334</v>
+        <v>46148.30208333334</v>
       </c>
       <c r="B30">
-        <v>824</v>
+        <v>786</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46146.3125</v>
+        <v>46148.3125</v>
       </c>
       <c r="B31">
-        <v>1011</v>
+        <v>992</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46146.32291666666</v>
+        <v>46148.32291666666</v>
       </c>
       <c r="B32">
-        <v>1168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46146.33333333334</v>
+        <v>46148.33333333334</v>
       </c>
       <c r="B33">
-        <v>1322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46146.34375</v>
+        <v>46148.34375</v>
       </c>
       <c r="B34">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46146.35416666666</v>
+        <v>46148.35416666666</v>
       </c>
       <c r="B35">
-        <v>1576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46146.36458333334</v>
+        <v>46148.36458333334</v>
       </c>
       <c r="B36">
-        <v>1728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46146.375</v>
+        <v>46148.375</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46146.38541666666</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46146.39583333334</v>
+        <v>46148.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46146.40625</v>
+        <v>46148.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46146.41666666666</v>
+        <v>46148.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46146.42708333334</v>
+        <v>46148.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46146.4375</v>
+        <v>46148.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46146.44791666666</v>
+        <v>46148.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46146.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46146.46875</v>
+        <v>46148.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46146.47916666666</v>
+        <v>46148.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46146.48958333334</v>
+        <v>46148.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46146.5</v>
+        <v>46148.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46146.51041666666</v>
+        <v>46148.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46146.52083333334</v>
+        <v>46148.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46146.53125</v>
+        <v>46148.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46146.54166666666</v>
+        <v>46148.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46146.55208333334</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46146.5625</v>
+        <v>46148.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46146.57291666666</v>
+        <v>46148.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46146.58333333334</v>
+        <v>46148.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46146.59375</v>
+        <v>46148.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46146.60416666666</v>
+        <v>46148.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46146.61458333334</v>
+        <v>46148.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46146.625</v>
+        <v>46148.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46146.63541666666</v>
+        <v>46148.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46146.64583333334</v>
+        <v>46148.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46146.65625</v>
+        <v>46148.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46146.66666666666</v>
+        <v>46148.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46146.67708333334</v>
+        <v>46148.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46146.6875</v>
+        <v>46148.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46146.69791666666</v>
+        <v>46148.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46146.70833333334</v>
+        <v>46148.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46146.71875</v>
+        <v>46148.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46146.72916666666</v>
+        <v>46148.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46146.73958333334</v>
+        <v>46148.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46146.75</v>
+        <v>46148.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46146.76041666666</v>
+        <v>46148.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46146.77083333334</v>
+        <v>46148.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46146.78125</v>
+        <v>46148.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46146.79166666666</v>
+        <v>46148.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46146.80208333334</v>
+        <v>46148.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46146.8125</v>
+        <v>46148.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46146.82291666666</v>
+        <v>46148.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46146.83333333334</v>
+        <v>46148.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46146.84375</v>
+        <v>46148.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46146.85416666666</v>
+        <v>46148.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46146.86458333334</v>
+        <v>46148.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46146.875</v>
+        <v>46148.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46146.88541666666</v>
+        <v>46148.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46146.89583333334</v>
+        <v>46148.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46146.90625</v>
+        <v>46148.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46146.91666666666</v>
+        <v>46148.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46146.92708333334</v>
+        <v>46148.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46146.9375</v>
+        <v>46148.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46146.94791666666</v>
+        <v>46148.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46146.95833333334</v>
+        <v>46148.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46146.96875</v>
+        <v>46148.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46146.97916666666</v>
+        <v>46148.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46146.98958333334</v>
+        <v>46148.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,103 +562,103 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B24">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B25">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B26">
-        <v>211</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B27">
-        <v>334</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B28">
-        <v>469</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B29">
-        <v>629</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B30">
-        <v>786</v>
+        <v>538</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B31">
-        <v>992</v>
+        <v>664</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>822</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>921</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46150.01041666666</v>
+        <v>46153</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46150.02083333334</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46150.03125</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46150.04166666666</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46150.05208333334</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46150.0625</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46150.07291666666</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46150.08333333334</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46150.09375</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46150.10416666666</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46150.11458333334</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46150.125</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46150.13541666666</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46150.14583333334</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46150.15625</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46150.16666666666</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46150.17708333334</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46150.1875</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46150.19791666666</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46150.20833333334</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,471 +554,471 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46150.21875</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46150.22916666666</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46150.23958333334</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46150.25</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>91</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46150.26041666666</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>148</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46150.27083333334</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>236</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46150.28125</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>342</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46150.29166666666</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>426</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46150.30208333334</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>538</v>
+        <v>750</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46150.3125</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>664</v>
+        <v>917</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46150.32291666666</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>822</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46150.33333333334</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>921</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46150.34375</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>1021</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46150.35416666666</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46150.36458333334</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46150.375</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46150.38541666666</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46150.39583333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46150.40625</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46150.41666666666</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46150.42708333334</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46150.4375</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46150.44791666666</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46150.45833333334</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46150.46875</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46150.47916666666</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46150.48958333334</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46150.5</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46150.51041666666</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46150.52083333334</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46150.53125</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46150.54166666666</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46150.55208333334</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46150.5625</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46150.57291666666</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46150.58333333334</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46150.59375</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46150.60416666666</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46150.61458333334</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46150.625</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46150.63541666666</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46150.64583333334</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46150.65625</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46150.66666666666</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46150.67708333334</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46150.6875</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46150.69791666666</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>997</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46150.70833333334</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>944</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46150.71875</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>879</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46150.72916666666</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>715</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46150.73958333334</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>572</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46150.75</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>456</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46150.76041666666</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46150.77083333334</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46150.78125</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46150.79166666666</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46150.80208333334</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46150.8125</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46150.82291666666</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46150.83333333334</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46150.84375</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46150.85416666666</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46150.86458333334</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46150.875</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46150.88541666666</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46150.89583333334</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46150.90625</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46150.91666666666</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46150.92708333334</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46150.9375</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46150.94791666666</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46150.95833333334</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46150.96875</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46150.97916666666</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46150.98958333334</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46151</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46154.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46154.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46154.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46154.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46154.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46154.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46154.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46154.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46154.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46154.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46154.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46154.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46154.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46154.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46154.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46154.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46154.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46154.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46154.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46154.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46154.21875</v>
+      </c>
+      <c r="B119">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46154.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46154.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46154.25</v>
+      </c>
+      <c r="B122">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46154.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46154.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46154.28125</v>
+      </c>
+      <c r="B125">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46154.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46154.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46154.3125</v>
+      </c>
+      <c r="B128">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46154.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46154.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46154.34375</v>
+      </c>
+      <c r="B131">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46154.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46154.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46154.375</v>
+      </c>
+      <c r="B134">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46154.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46154.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46154.40625</v>
+      </c>
+      <c r="B137">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46154.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46154.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46154.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46154.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46154.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46154.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46154.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46154.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46154.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46154.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46154.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46154.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46154.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46154.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46154.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46154.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46154.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46154.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46154.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46154.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46154.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46154.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46154.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46154.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46154.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46154.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46154.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46154.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46154.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46154.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46154.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46154.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46154.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46154.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46154.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46154.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46154.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46154.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46154.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46154.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46154.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46154.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46154.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46154.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46154.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46154.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46154.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46154.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46154.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46154.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46154.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46154.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46154.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46154.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46154.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46154.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,479 +554,479 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>81</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>143</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>220</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>337</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>470</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>613</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>750</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>917</v>
+        <v>522</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>1029</v>
+        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>1117</v>
+        <v>781</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>1269</v>
+        <v>859</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>1381</v>
+        <v>926</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>1472</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>1532</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>1582</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>1684</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>1822</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>1819</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>1830</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>1869</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>1858</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>1922</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>1894</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>1955</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>1993</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>1967</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>1965</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>1992</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>1998</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>2009</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>1887</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>1773</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>1721</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>1687</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>1619</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>1599</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>1500</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>1480</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>1433</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>1405</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>1361</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>1242</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>1159</v>
+        <v>934</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>1083</v>
+        <v>933</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>997</v>
+        <v>854</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>944</v>
+        <v>752</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>879</v>
+        <v>650</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>715</v>
+        <v>562</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>572</v>
+        <v>480</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>456</v>
+        <v>394</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>342</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>139</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -1322,183 +1322,183 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>100</v>
+        <v>131</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>400</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>515</v>
+        <v>484</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>632</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>735</v>
+        <v>746</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>797</v>
+        <v>897</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>908</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>939</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>974</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>1068</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>1134</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>1168</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>1163</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>1239</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>1244</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>1413</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>1496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46157.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46157.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46157.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46157.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46157.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46157.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,479 +554,479 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46157.21875</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B24">
-        <v>34</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46157.25</v>
       </c>
       <c r="B25">
-        <v>73</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B26">
-        <v>137</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B27">
-        <v>211</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46157.28125</v>
       </c>
       <c r="B28">
-        <v>297</v>
+        <v>575</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B29">
-        <v>364</v>
+        <v>701</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B30">
-        <v>448</v>
+        <v>818</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46157.3125</v>
       </c>
       <c r="B31">
-        <v>522</v>
+        <v>980</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B32">
-        <v>649</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B33">
-        <v>781</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46157.34375</v>
       </c>
       <c r="B34">
-        <v>859</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B35">
-        <v>926</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B36">
-        <v>1002</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46157.375</v>
       </c>
       <c r="B37">
-        <v>1048</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B38">
-        <v>1074</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B39">
-        <v>1153</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46157.40625</v>
       </c>
       <c r="B40">
-        <v>1145</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B41">
-        <v>1176</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B42">
-        <v>1254</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46157.4375</v>
       </c>
       <c r="B43">
-        <v>1285</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B44">
-        <v>1334</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B45">
-        <v>1359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46157.46875</v>
       </c>
       <c r="B46">
-        <v>1398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B47">
-        <v>1452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B48">
-        <v>1446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46157.5</v>
       </c>
       <c r="B49">
-        <v>1391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B50">
-        <v>1369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B51">
-        <v>1390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46157.53125</v>
       </c>
       <c r="B52">
-        <v>1393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B53">
-        <v>1355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B54">
-        <v>1380</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46157.5625</v>
       </c>
       <c r="B55">
-        <v>1440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B56">
-        <v>1392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B57">
-        <v>1375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46157.59375</v>
       </c>
       <c r="B58">
-        <v>1353</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B59">
-        <v>1347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B60">
-        <v>1257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46157.625</v>
       </c>
       <c r="B61">
-        <v>1360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B62">
-        <v>1245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B63">
-        <v>1187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46157.65625</v>
       </c>
       <c r="B64">
-        <v>1151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B65">
-        <v>1028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B66">
-        <v>934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46157.6875</v>
       </c>
       <c r="B67">
-        <v>933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B68">
-        <v>854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B69">
-        <v>752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46157.71875</v>
       </c>
       <c r="B70">
-        <v>650</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B71">
-        <v>562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B72">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46157.75</v>
       </c>
       <c r="B73">
-        <v>394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B74">
-        <v>308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B75">
-        <v>234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46157.78125</v>
       </c>
       <c r="B76">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B77">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B78">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46157.8125</v>
       </c>
       <c r="B79">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B80">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46157.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46157.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46157.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46157.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46157.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,777 +1154,9 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46158</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="2">
-        <v>46156</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="2">
-        <v>46156.01041666666</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="2">
-        <v>46156.02083333334</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="2">
-        <v>46156.03125</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="2">
-        <v>46156.04166666666</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="2">
-        <v>46156.05208333334</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="2">
-        <v>46156.0625</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="2">
-        <v>46156.07291666666</v>
-      </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="2">
-        <v>46156.08333333334</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="2">
-        <v>46156.09375</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="2">
-        <v>46156.10416666666</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="2">
-        <v>46156.11458333334</v>
-      </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="2">
-        <v>46156.125</v>
-      </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="2">
-        <v>46156.13541666666</v>
-      </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="2">
-        <v>46156.14583333334</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="2">
-        <v>46156.15625</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="2">
-        <v>46156.16666666666</v>
-      </c>
-      <c r="B114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="2">
-        <v>46156.17708333334</v>
-      </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2">
-        <v>46156.1875</v>
-      </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="2">
-        <v>46156.19791666666</v>
-      </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="2">
-        <v>46156.20833333334</v>
-      </c>
-      <c r="B118">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="2">
-        <v>46156.21875</v>
-      </c>
-      <c r="B119">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="2">
-        <v>46156.22916666666</v>
-      </c>
-      <c r="B120">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="2">
-        <v>46156.23958333334</v>
-      </c>
-      <c r="B121">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>46156.25</v>
-      </c>
-      <c r="B122">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="2">
-        <v>46156.26041666666</v>
-      </c>
-      <c r="B123">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="2">
-        <v>46156.27083333334</v>
-      </c>
-      <c r="B124">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="2">
-        <v>46156.28125</v>
-      </c>
-      <c r="B125">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="2">
-        <v>46156.29166666666</v>
-      </c>
-      <c r="B126">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="2">
-        <v>46156.30208333334</v>
-      </c>
-      <c r="B127">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="2">
-        <v>46156.3125</v>
-      </c>
-      <c r="B128">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>46156.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>46156.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="2">
-        <v>46156.34375</v>
-      </c>
-      <c r="B131">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="2">
-        <v>46156.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46156.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="2">
-        <v>46156.375</v>
-      </c>
-      <c r="B134">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="2">
-        <v>46156.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="2">
-        <v>46156.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="2">
-        <v>46156.40625</v>
-      </c>
-      <c r="B137">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="2">
-        <v>46156.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="2">
-        <v>46156.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="2">
-        <v>46156.4375</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="2">
-        <v>46156.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46156.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46156.46875</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46156.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46156.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46156.5</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46156.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46156.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46156.53125</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46156.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46156.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46156.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46156.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46156.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46156.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46156.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46156.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46156.625</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46156.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46156.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46156.65625</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46156.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46156.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46156.6875</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46156.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46156.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46156.71875</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46156.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46156.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46156.75</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46156.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46156.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46156.78125</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46156.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46156.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46156.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46156.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46156.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46156.84375</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46156.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46156.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46156.875</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46156.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46156.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46156.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46156.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46156.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46156.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46156.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46156.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46156.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46156.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46156.98958333334</v>
-      </c>
-      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,263 +554,263 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B23">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B24">
-        <v>108</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B25">
-        <v>179</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B26">
-        <v>283</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B27">
-        <v>415</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B28">
-        <v>575</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B29">
-        <v>701</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B30">
-        <v>818</v>
+        <v>530</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B31">
-        <v>980</v>
+        <v>608</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B32">
-        <v>1113</v>
+        <v>704</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B33">
-        <v>1269</v>
+        <v>801</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B34">
-        <v>1398</v>
+        <v>876</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B35">
-        <v>1487</v>
+        <v>979</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B36">
-        <v>1599</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B37">
-        <v>1662</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B38">
-        <v>1675</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B39">
-        <v>1783</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B40">
-        <v>1846</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B41">
-        <v>1880</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B42">
-        <v>1951</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B43">
-        <v>2046</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B44">
-        <v>2098</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46158</v>
+        <v>46164</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -562,255 +562,255 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B23">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B24">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B25">
-        <v>97</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B26">
-        <v>153</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B27">
-        <v>225</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B28">
-        <v>316</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B29">
-        <v>422</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B30">
-        <v>530</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B31">
-        <v>608</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B32">
-        <v>704</v>
+        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B33">
-        <v>801</v>
+        <v>519</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B34">
-        <v>876</v>
+        <v>641</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B35">
-        <v>979</v>
+        <v>648</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B36">
-        <v>1094</v>
+        <v>723</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B37">
-        <v>1179</v>
+        <v>852</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B38">
-        <v>1231</v>
+        <v>910</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B39">
-        <v>1308</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B40">
-        <v>1367</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B41">
-        <v>1369</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B42">
-        <v>1346</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B43">
-        <v>1379</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B44">
-        <v>1374</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B45">
-        <v>1406</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B46">
-        <v>1379</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B47">
-        <v>1361</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B48">
-        <v>1308</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B49">
-        <v>1264</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B50">
-        <v>1289</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B51">
-        <v>1333</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B52">
-        <v>1261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B53">
-        <v>1283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46164.01041666666</v>
+        <v>46167.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46164.02083333334</v>
+        <v>46167.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46164.03125</v>
+        <v>46167.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46164.04166666666</v>
+        <v>46167.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46164.05208333334</v>
+        <v>46167.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46164.0625</v>
+        <v>46167.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46164.07291666666</v>
+        <v>46167.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46164.08333333334</v>
+        <v>46167.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46164.09375</v>
+        <v>46167.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46164.10416666666</v>
+        <v>46167.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46164.11458333334</v>
+        <v>46167.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46164.125</v>
+        <v>46167.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46164.13541666666</v>
+        <v>46167.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46164.14583333334</v>
+        <v>46167.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46164.15625</v>
+        <v>46167.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46164.16666666666</v>
+        <v>46167.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46164.17708333334</v>
+        <v>46167.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46164.1875</v>
+        <v>46167.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46164.19791666666</v>
+        <v>46167.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,255 +546,255 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46164.20833333334</v>
+        <v>46167.20833333334</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46164.21875</v>
+        <v>46167.21875</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46164.22916666666</v>
+        <v>46167.22916666666</v>
       </c>
       <c r="B23">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46164.23958333334</v>
+        <v>46167.23958333334</v>
       </c>
       <c r="B24">
-        <v>42</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46164.25</v>
+        <v>46167.25</v>
       </c>
       <c r="B25">
-        <v>71</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46164.26041666666</v>
+        <v>46167.26041666666</v>
       </c>
       <c r="B26">
-        <v>95</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46164.27083333334</v>
+        <v>46167.27083333334</v>
       </c>
       <c r="B27">
-        <v>136</v>
+        <v>491</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46164.28125</v>
+        <v>46167.28125</v>
       </c>
       <c r="B28">
-        <v>193</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46164.29166666666</v>
+        <v>46167.29166666666</v>
       </c>
       <c r="B29">
-        <v>243</v>
+        <v>773</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46164.30208333334</v>
+        <v>46167.30208333334</v>
       </c>
       <c r="B30">
-        <v>304</v>
+        <v>972</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46164.3125</v>
+        <v>46167.3125</v>
       </c>
       <c r="B31">
-        <v>384</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46164.32291666666</v>
+        <v>46167.32291666666</v>
       </c>
       <c r="B32">
-        <v>416</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46164.33333333334</v>
+        <v>46167.33333333334</v>
       </c>
       <c r="B33">
-        <v>519</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46164.34375</v>
+        <v>46167.34375</v>
       </c>
       <c r="B34">
-        <v>641</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46164.35416666666</v>
+        <v>46167.35416666666</v>
       </c>
       <c r="B35">
-        <v>648</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46164.36458333334</v>
+        <v>46167.36458333334</v>
       </c>
       <c r="B36">
-        <v>723</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46164.375</v>
+        <v>46167.375</v>
       </c>
       <c r="B37">
-        <v>852</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46164.38541666666</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="B38">
-        <v>910</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46164.39583333334</v>
+        <v>46167.39583333334</v>
       </c>
       <c r="B39">
-        <v>1087</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46164.40625</v>
+        <v>46167.40625</v>
       </c>
       <c r="B40">
-        <v>1186</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46164.41666666666</v>
+        <v>46167.41666666666</v>
       </c>
       <c r="B41">
-        <v>1153</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46164.42708333334</v>
+        <v>46167.42708333334</v>
       </c>
       <c r="B42">
-        <v>1145</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46164.4375</v>
+        <v>46167.4375</v>
       </c>
       <c r="B43">
-        <v>1194</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46164.44791666666</v>
+        <v>46167.44791666666</v>
       </c>
       <c r="B44">
-        <v>1155</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46164.45833333334</v>
+        <v>46167.45833333334</v>
       </c>
       <c r="B45">
-        <v>1251</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46164.46875</v>
+        <v>46167.46875</v>
       </c>
       <c r="B46">
-        <v>1333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46164.47916666666</v>
+        <v>46167.47916666666</v>
       </c>
       <c r="B47">
-        <v>1323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46164.48958333334</v>
+        <v>46167.48958333334</v>
       </c>
       <c r="B48">
-        <v>1371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46164.5</v>
+        <v>46167.5</v>
       </c>
       <c r="B49">
-        <v>1341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46164.51041666666</v>
+        <v>46167.51041666666</v>
       </c>
       <c r="B50">
-        <v>1236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46164.52083333334</v>
+        <v>46167.52083333334</v>
       </c>
       <c r="B51">
-        <v>1302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46164.53125</v>
+        <v>46167.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46164.54166666666</v>
+        <v>46167.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46164.55208333334</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46164.5625</v>
+        <v>46167.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46164.57291666666</v>
+        <v>46167.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46164.58333333334</v>
+        <v>46167.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46164.59375</v>
+        <v>46167.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46164.60416666666</v>
+        <v>46167.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46164.61458333334</v>
+        <v>46167.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46164.625</v>
+        <v>46167.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46164.63541666666</v>
+        <v>46167.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46164.64583333334</v>
+        <v>46167.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46164.65625</v>
+        <v>46167.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46164.66666666666</v>
+        <v>46167.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46164.67708333334</v>
+        <v>46167.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46164.6875</v>
+        <v>46167.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46164.69791666666</v>
+        <v>46167.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46164.70833333334</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46164.71875</v>
+        <v>46167.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46164.72916666666</v>
+        <v>46167.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46164.73958333334</v>
+        <v>46167.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46164.75</v>
+        <v>46167.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46164.76041666666</v>
+        <v>46167.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46164.77083333334</v>
+        <v>46167.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46164.78125</v>
+        <v>46167.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46164.79166666666</v>
+        <v>46167.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46164.80208333334</v>
+        <v>46167.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46164.8125</v>
+        <v>46167.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46164.82291666666</v>
+        <v>46167.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46164.83333333334</v>
+        <v>46167.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46164.84375</v>
+        <v>46167.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46164.85416666666</v>
+        <v>46167.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46164.86458333334</v>
+        <v>46167.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46164.875</v>
+        <v>46167.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46164.88541666666</v>
+        <v>46167.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46164.89583333334</v>
+        <v>46167.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46164.90625</v>
+        <v>46167.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46164.91666666666</v>
+        <v>46167.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46164.92708333334</v>
+        <v>46167.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46164.9375</v>
+        <v>46167.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46164.94791666666</v>
+        <v>46167.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46164.95833333334</v>
+        <v>46167.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46164.96875</v>
+        <v>46167.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46164.97916666666</v>
+        <v>46167.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46164.98958333334</v>
+        <v>46167.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,207 +546,207 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B22">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B23">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B24">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B25">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B26">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B27">
-        <v>491</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B28">
-        <v>595</v>
+        <v>615</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B29">
-        <v>773</v>
+        <v>784</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B30">
-        <v>972</v>
+        <v>995</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B31">
-        <v>1160</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B32">
-        <v>1333</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B33">
-        <v>1494</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B34">
-        <v>1607</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B35">
-        <v>1740</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B36">
-        <v>1869</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B37">
-        <v>1991</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B38">
-        <v>2075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B39">
-        <v>2125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B40">
-        <v>2009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B41">
-        <v>1909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B42">
-        <v>2066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B43">
-        <v>2204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B44">
-        <v>2220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B45">
-        <v>2194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168.01041666666</v>
+        <v>46168</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.02083333334</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.03125</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.04166666666</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.05208333334</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.0625</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.07291666666</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.08333333334</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.09375</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.10416666666</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.11458333334</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.125</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.13541666666</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.14583333334</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.15625</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.16666666666</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.17708333334</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.1875</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.19791666666</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.20833333334</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.21875</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
         <v>29</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.22916666666</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
         <v>78</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.23958333334</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
         <v>149</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.25</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
         <v>236</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.26041666666</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
         <v>337</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.27083333334</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
         <v>462</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.28125</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
         <v>615</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.29166666666</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
         <v>784</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.30208333334</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
         <v>995</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.3125</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
         <v>1198</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.32291666666</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
         <v>1350</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.33333333334</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
         <v>1507</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.34375</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
         <v>1658</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.35416666666</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
         <v>1787</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.36458333334</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
         <v>1886</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.375</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
         <v>1979</v>
@@ -682,367 +682,367 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.38541666666</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.39583333334</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.40625</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.41666666666</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.42708333334</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.4375</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.44791666666</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.45833333334</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.46875</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.47916666666</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.48958333334</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.5</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.51041666666</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.52083333334</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.53125</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.54166666666</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.55208333334</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.5625</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.57291666666</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.58333333334</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.59375</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.60416666666</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.61458333334</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.625</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.63541666666</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.64583333334</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.65625</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.66666666666</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.67708333334</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.6875</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.69791666666</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.70833333334</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.71875</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.72916666666</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.73958333334</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>942</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.75</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>779</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.76041666666</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>603</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.77083333334</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.78125</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.79166666666</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.80208333334</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.8125</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.82291666666</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.83333333334</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.84375</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.85416666666</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.86458333334</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.875</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.88541666666</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.89583333334</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.90625</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.91666666666</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.92708333334</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.9375</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.94791666666</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.95833333334</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.96875</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.97916666666</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.98958333334</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,9 +1154,777 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
+        <v>46168.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>46169</v>
       </c>
-      <c r="B97">
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46169.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46169.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46169.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46169.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46169.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46169.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46169.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46169.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46169.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46169.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46169.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46169.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46169.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46169.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46169.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46169.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46169.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46169.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46169.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46169.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46169.21875</v>
+      </c>
+      <c r="B119">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46169.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46169.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46169.25</v>
+      </c>
+      <c r="B122">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46169.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46169.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46169.28125</v>
+      </c>
+      <c r="B125">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46169.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46169.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46169.3125</v>
+      </c>
+      <c r="B128">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46169.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46169.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46169.34375</v>
+      </c>
+      <c r="B131">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46169.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46169.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46169.375</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46169.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46169.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46169.40625</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46169.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46169.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46169.4375</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46169.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46169.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46169.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46169.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46169.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46169.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46169.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46169.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46169.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46169.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46169.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46169.5625</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46169.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46169.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46169.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46169.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46169.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46169.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46169.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46169.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46169.65625</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46169.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46169.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46169.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46169.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46169.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46169.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46169.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46169.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46169.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46169.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46169.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46169.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46169.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46169.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46169.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46169.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46169.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46169.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46169.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46169.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46169.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46169.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46169.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46169.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46169.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46169.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46169.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46169.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46169.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46169.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46169.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46169.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,15 +546,15 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
         <v>29</v>
@@ -562,15 +562,15 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
         <v>149</v>
@@ -578,471 +578,471 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>462</v>
+        <v>473</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>615</v>
+        <v>625</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>784</v>
+        <v>794</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>995</v>
+        <v>967</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>1198</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>1350</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>1507</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>1658</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>1787</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>1886</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>1979</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>2068</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>2148</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>2216</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>2286</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>2305</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>2255</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>2257</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>2287</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>2176</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>2173</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>2188</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>2149</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>2184</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>2174</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>2214</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>2212</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>2156</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>2184</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>2201</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>2236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>2200</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>2161</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>2142</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>2113</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>2014</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>1959</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>1905</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>1858</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>1754</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>1740</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>1633</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>1499</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>1316</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>1131</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>942</v>
+        <v>863</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>779</v>
+        <v>702</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>603</v>
+        <v>533</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>440</v>
+        <v>398</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
         <v>2</v>
@@ -1322,127 +1322,127 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>149</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>234</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>338</v>
+        <v>287</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>625</v>
+        <v>596</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>794</v>
+        <v>750</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>967</v>
+        <v>917</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>1152</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>1300</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>1464</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>1605</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>1733</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -554,487 +554,487 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>149</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>234</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>338</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>625</v>
+        <v>596</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>794</v>
+        <v>750</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>967</v>
+        <v>917</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>1152</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>1300</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>1464</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>1605</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>1733</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>1844</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>1933</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>2014</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>2100</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>2174</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>2209</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>2256</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>2300</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>2303</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>2351</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>2371</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>2434</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>2425</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>2414</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>2482</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>2492</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>2479</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>2475</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>2424</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>2401</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>2379</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>2398</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>2371</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>2328</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>2302</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>2199</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>2115</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>2031</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>1959</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>1824</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>1692</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>1549</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>1409</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>1244</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>1077</v>
+        <v>972</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>863</v>
+        <v>784</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>702</v>
+        <v>642</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>533</v>
+        <v>488</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>398</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>291</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -1314,135 +1314,135 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>121</v>
+        <v>160</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>197</v>
+        <v>247</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>287</v>
+        <v>355</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>463</v>
+        <v>503</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>596</v>
+        <v>650</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>750</v>
+        <v>843</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>917</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>1075</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>1172</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>1289</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>1431</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>1552</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>1678</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -1594,7 +1594,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,495 +546,495 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B22">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B23">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B24">
-        <v>121</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B25">
-        <v>197</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B26">
-        <v>287</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B27">
-        <v>463</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B28">
-        <v>596</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B29">
-        <v>750</v>
+        <v>843</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B30">
-        <v>917</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B31">
-        <v>1075</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B32">
-        <v>1172</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B33">
-        <v>1289</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B34">
-        <v>1431</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B35">
-        <v>1552</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B36">
-        <v>1678</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B37">
-        <v>1753</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B38">
-        <v>1875</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B39">
-        <v>1967</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B40">
-        <v>1929</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B41">
-        <v>1995</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B42">
-        <v>2031</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B43">
-        <v>2119</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B44">
-        <v>2115</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B45">
-        <v>2066</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B46">
-        <v>2051</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B47">
-        <v>2072</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B48">
-        <v>1899</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B49">
-        <v>1920</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B50">
-        <v>1963</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B51">
-        <v>1970</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B52">
-        <v>1957</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B53">
-        <v>2017</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B54">
-        <v>2079</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B55">
-        <v>1968</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B56">
-        <v>1860</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B57">
-        <v>1816</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B58">
-        <v>1781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B59">
-        <v>1842</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B60">
-        <v>1812</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B61">
-        <v>1840</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B62">
-        <v>1744</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B63">
-        <v>1645</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B64">
-        <v>1625</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B65">
-        <v>1544</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B66">
-        <v>1571</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B67">
-        <v>1386</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B68">
-        <v>1306</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B69">
-        <v>1185</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B70">
-        <v>1066</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B71">
-        <v>972</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B72">
-        <v>784</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B73">
-        <v>642</v>
+        <v>842</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B74">
-        <v>488</v>
+        <v>647</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B75">
-        <v>367</v>
+        <v>463</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B76">
-        <v>260</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B77">
-        <v>183</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B78">
-        <v>116</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B79">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B80">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46171.01041666666</v>
+        <v>46172.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46171.02083333334</v>
+        <v>46172.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46171.03125</v>
+        <v>46172.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46171.04166666666</v>
+        <v>46172.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46171.05208333334</v>
+        <v>46172.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46171.0625</v>
+        <v>46172.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46171.07291666666</v>
+        <v>46172.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46171.08333333334</v>
+        <v>46172.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46171.09375</v>
+        <v>46172.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46171.10416666666</v>
+        <v>46172.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46171.11458333334</v>
+        <v>46172.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46171.125</v>
+        <v>46172.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46171.13541666666</v>
+        <v>46172.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46171.14583333334</v>
+        <v>46172.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46171.15625</v>
+        <v>46172.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46171.16666666666</v>
+        <v>46172.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46171.17708333334</v>
+        <v>46172.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46171.1875</v>
+        <v>46172.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -1314,487 +1314,487 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46171.19791666666</v>
+        <v>46172.19791666666</v>
       </c>
       <c r="B117">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46171.20833333334</v>
+        <v>46172.20833333334</v>
       </c>
       <c r="B118">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46171.21875</v>
+        <v>46172.21875</v>
       </c>
       <c r="B119">
-        <v>97</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46171.22916666666</v>
+        <v>46172.22916666666</v>
       </c>
       <c r="B120">
-        <v>160</v>
+        <v>84</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46171.23958333334</v>
+        <v>46172.23958333334</v>
       </c>
       <c r="B121">
-        <v>247</v>
+        <v>138</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46171.25</v>
+        <v>46172.25</v>
       </c>
       <c r="B122">
-        <v>355</v>
+        <v>231</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46171.26041666666</v>
+        <v>46172.26041666666</v>
       </c>
       <c r="B123">
-        <v>503</v>
+        <v>327</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46171.27083333334</v>
+        <v>46172.27083333334</v>
       </c>
       <c r="B124">
-        <v>650</v>
+        <v>462</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46171.28125</v>
+        <v>46172.28125</v>
       </c>
       <c r="B125">
-        <v>843</v>
+        <v>575</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46171.29166666666</v>
+        <v>46172.29166666666</v>
       </c>
       <c r="B126">
-        <v>1058</v>
+        <v>727</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46171.30208333334</v>
+        <v>46172.30208333334</v>
       </c>
       <c r="B127">
-        <v>1243</v>
+        <v>857</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46171.3125</v>
+        <v>46172.3125</v>
       </c>
       <c r="B128">
-        <v>1425</v>
+        <v>988</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46171.32291666666</v>
+        <v>46172.32291666666</v>
       </c>
       <c r="B129">
-        <v>1626</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46171.33333333334</v>
+        <v>46172.33333333334</v>
       </c>
       <c r="B130">
-        <v>1784</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46171.34375</v>
+        <v>46172.34375</v>
       </c>
       <c r="B131">
-        <v>1915</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46171.35416666666</v>
+        <v>46172.35416666666</v>
       </c>
       <c r="B132">
-        <v>2021</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46171.36458333334</v>
+        <v>46172.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46171.375</v>
+        <v>46172.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46171.38541666666</v>
+        <v>46172.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46171.39583333334</v>
+        <v>46172.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46171.40625</v>
+        <v>46172.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46171.41666666666</v>
+        <v>46172.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46171.42708333334</v>
+        <v>46172.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46171.4375</v>
+        <v>46172.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46171.44791666666</v>
+        <v>46172.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46171.45833333334</v>
+        <v>46172.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46171.46875</v>
+        <v>46172.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46171.47916666666</v>
+        <v>46172.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46171.48958333334</v>
+        <v>46172.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46171.5</v>
+        <v>46172.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46171.51041666666</v>
+        <v>46172.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46171.52083333334</v>
+        <v>46172.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46171.53125</v>
+        <v>46172.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46171.54166666666</v>
+        <v>46172.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46171.55208333334</v>
+        <v>46172.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46171.5625</v>
+        <v>46172.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46171.57291666666</v>
+        <v>46172.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46171.58333333334</v>
+        <v>46172.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46171.59375</v>
+        <v>46172.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46171.60416666666</v>
+        <v>46172.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46171.61458333334</v>
+        <v>46172.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46171.625</v>
+        <v>46172.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>908</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46171.63541666666</v>
+        <v>46172.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>809</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46171.64583333334</v>
+        <v>46172.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>814</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46171.65625</v>
+        <v>46172.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>791</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46171.66666666666</v>
+        <v>46172.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>967</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46171.67708333334</v>
+        <v>46172.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>990</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46171.6875</v>
+        <v>46172.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>949</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46171.69791666666</v>
+        <v>46172.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>901</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46171.70833333334</v>
+        <v>46172.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>854</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46171.71875</v>
+        <v>46172.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>802</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46171.72916666666</v>
+        <v>46172.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>627</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46171.73958333334</v>
+        <v>46172.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>533</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46171.75</v>
+        <v>46172.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46171.76041666666</v>
+        <v>46172.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46171.77083333334</v>
+        <v>46172.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46171.78125</v>
+        <v>46172.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46171.79166666666</v>
+        <v>46172.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46171.80208333334</v>
+        <v>46172.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46171.8125</v>
+        <v>46172.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46171.82291666666</v>
+        <v>46172.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46171.83333333334</v>
+        <v>46172.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46171.84375</v>
+        <v>46172.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46171.85416666666</v>
+        <v>46172.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46171.86458333334</v>
+        <v>46172.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46171.875</v>
+        <v>46172.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46171.88541666666</v>
+        <v>46172.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46171.89583333334</v>
+        <v>46172.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46171.90625</v>
+        <v>46172.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46171.91666666666</v>
+        <v>46172.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46171.92708333334</v>
+        <v>46172.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46171.9375</v>
+        <v>46172.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46171.94791666666</v>
+        <v>46172.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46171.95833333334</v>
+        <v>46172.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46171.96875</v>
+        <v>46172.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46171.97916666666</v>
+        <v>46172.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,9 +1922,3081 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46171.98958333334</v>
+        <v>46172.98958333334</v>
       </c>
       <c r="B193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46173.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46173.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46173.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46173.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46173.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46173.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46173.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46173.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46173.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46173.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46173.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46173.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46173.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46173.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46173.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46173.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46173.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46173.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46173.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46173.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46173.21875</v>
+      </c>
+      <c r="B215">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46173.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46173.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46173.25</v>
+      </c>
+      <c r="B218">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46173.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46173.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46173.28125</v>
+      </c>
+      <c r="B221">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46173.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46173.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46173.3125</v>
+      </c>
+      <c r="B224">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46173.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46173.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46173.34375</v>
+      </c>
+      <c r="B227">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46173.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46173.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46173.375</v>
+      </c>
+      <c r="B230">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46173.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46173.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46173.40625</v>
+      </c>
+      <c r="B233">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46173.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46173.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46173.4375</v>
+      </c>
+      <c r="B236">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46173.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46173.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46173.46875</v>
+      </c>
+      <c r="B239">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46173.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46173.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46173.5</v>
+      </c>
+      <c r="B242">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46173.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46173.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46173.53125</v>
+      </c>
+      <c r="B245">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46173.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46173.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46173.5625</v>
+      </c>
+      <c r="B248">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46173.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46173.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46173.59375</v>
+      </c>
+      <c r="B251">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46173.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46173.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46173.625</v>
+      </c>
+      <c r="B254">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46173.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46173.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46173.65625</v>
+      </c>
+      <c r="B257">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46173.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46173.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46173.6875</v>
+      </c>
+      <c r="B260">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46173.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46173.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46173.71875</v>
+      </c>
+      <c r="B263">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46173.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46173.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46173.75</v>
+      </c>
+      <c r="B266">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46173.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46173.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46173.78125</v>
+      </c>
+      <c r="B269">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46173.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46173.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46173.8125</v>
+      </c>
+      <c r="B272">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46173.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46173.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46173.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46173.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46173.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46173.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46173.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46173.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46173.90625</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46173.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46173.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46173.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46173.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46173.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46173.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46173.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46173.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46174.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46174.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46174.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46174.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46174.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46174.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46174.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46174.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46174.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46174.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46174.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46174.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46174.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46174.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46174.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46174.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46174.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46174.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46174.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46174.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46174.21875</v>
+      </c>
+      <c r="B311">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46174.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46174.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46174.25</v>
+      </c>
+      <c r="B314">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46174.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46174.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46174.28125</v>
+      </c>
+      <c r="B317">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46174.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46174.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46174.3125</v>
+      </c>
+      <c r="B320">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46174.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46174.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46174.34375</v>
+      </c>
+      <c r="B323">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46174.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46174.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46174.375</v>
+      </c>
+      <c r="B326">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46174.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46174.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46174.40625</v>
+      </c>
+      <c r="B329">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46174.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46174.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46174.4375</v>
+      </c>
+      <c r="B332">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46174.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46174.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46174.46875</v>
+      </c>
+      <c r="B335">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46174.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46174.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46174.5</v>
+      </c>
+      <c r="B338">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46174.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46174.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46174.53125</v>
+      </c>
+      <c r="B341">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46174.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46174.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46174.5625</v>
+      </c>
+      <c r="B344">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46174.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46174.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46174.59375</v>
+      </c>
+      <c r="B347">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46174.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46174.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46174.625</v>
+      </c>
+      <c r="B350">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46174.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46174.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46174.65625</v>
+      </c>
+      <c r="B353">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46174.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46174.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46174.6875</v>
+      </c>
+      <c r="B356">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46174.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46174.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46174.71875</v>
+      </c>
+      <c r="B359">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46174.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46174.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46174.75</v>
+      </c>
+      <c r="B362">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46174.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46174.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46174.78125</v>
+      </c>
+      <c r="B365">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46174.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46174.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46174.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46174.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46174.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46174.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46174.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46174.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46174.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46174.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46174.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46174.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46174.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46174.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46174.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46174.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46174.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46174.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46174.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46174.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46175.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46175.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46175.03125</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46175.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46175.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46175.0625</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46175.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46175.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46175.09375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46175.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46175.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46175.125</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46175.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46175.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46175.15625</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46175.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46175.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46175.1875</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46175.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46175.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46175.21875</v>
+      </c>
+      <c r="B407">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46175.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46175.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46175.25</v>
+      </c>
+      <c r="B410">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46175.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46175.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46175.28125</v>
+      </c>
+      <c r="B413">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46175.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46175.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46175.3125</v>
+      </c>
+      <c r="B416">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46175.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46175.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46175.34375</v>
+      </c>
+      <c r="B419">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46175.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46175.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46175.375</v>
+      </c>
+      <c r="B422">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46175.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46175.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46175.40625</v>
+      </c>
+      <c r="B425">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46175.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46175.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46175.4375</v>
+      </c>
+      <c r="B428">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46175.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46175.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46175.46875</v>
+      </c>
+      <c r="B431">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46175.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46175.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46175.5</v>
+      </c>
+      <c r="B434">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46175.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46175.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46175.53125</v>
+      </c>
+      <c r="B437">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46175.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46175.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46175.5625</v>
+      </c>
+      <c r="B440">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46175.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46175.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46175.59375</v>
+      </c>
+      <c r="B443">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46175.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46175.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46175.625</v>
+      </c>
+      <c r="B446">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46175.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46175.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46175.65625</v>
+      </c>
+      <c r="B449">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46175.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46175.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46175.6875</v>
+      </c>
+      <c r="B452">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46175.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46175.71875</v>
+      </c>
+      <c r="B455">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46175.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46175.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46175.75</v>
+      </c>
+      <c r="B458">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46175.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46175.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46175.78125</v>
+      </c>
+      <c r="B461">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46175.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46175.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46175.8125</v>
+      </c>
+      <c r="B464">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46175.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46175.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46175.84375</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46175.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46175.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46175.875</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46175.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
+        <v>46175.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
+        <v>46175.90625</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
+        <v>46175.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
+        <v>46175.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
+        <v>46175.9375</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>46175.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
+        <v>46175.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
+        <v>46175.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
+        <v>46175.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
+        <v>46175.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2">
+        <v>46176.01041666666</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2">
+        <v>46176.02083333334</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2">
+        <v>46176.03125</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="2">
+        <v>46176.04166666666</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="2">
+        <v>46176.05208333334</v>
+      </c>
+      <c r="B487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="2">
+        <v>46176.0625</v>
+      </c>
+      <c r="B488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="2">
+        <v>46176.07291666666</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="2">
+        <v>46176.08333333334</v>
+      </c>
+      <c r="B490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="2">
+        <v>46176.09375</v>
+      </c>
+      <c r="B491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="2">
+        <v>46176.10416666666</v>
+      </c>
+      <c r="B492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="2">
+        <v>46176.11458333334</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="2">
+        <v>46176.125</v>
+      </c>
+      <c r="B494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="2">
+        <v>46176.13541666666</v>
+      </c>
+      <c r="B495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="2">
+        <v>46176.14583333334</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="2">
+        <v>46176.15625</v>
+      </c>
+      <c r="B497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="2">
+        <v>46176.16666666666</v>
+      </c>
+      <c r="B498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="2">
+        <v>46176.17708333334</v>
+      </c>
+      <c r="B499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="2">
+        <v>46176.1875</v>
+      </c>
+      <c r="B500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="2">
+        <v>46176.19791666666</v>
+      </c>
+      <c r="B501">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="2">
+        <v>46176.20833333334</v>
+      </c>
+      <c r="B502">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="2">
+        <v>46176.21875</v>
+      </c>
+      <c r="B503">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="2">
+        <v>46176.22916666666</v>
+      </c>
+      <c r="B504">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="2">
+        <v>46176.23958333334</v>
+      </c>
+      <c r="B505">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="2">
+        <v>46176.25</v>
+      </c>
+      <c r="B506">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="2">
+        <v>46176.26041666666</v>
+      </c>
+      <c r="B507">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="2">
+        <v>46176.27083333334</v>
+      </c>
+      <c r="B508">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="2">
+        <v>46176.28125</v>
+      </c>
+      <c r="B509">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="2">
+        <v>46176.29166666666</v>
+      </c>
+      <c r="B510">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2">
+        <v>46176.30208333334</v>
+      </c>
+      <c r="B511">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="2">
+        <v>46176.3125</v>
+      </c>
+      <c r="B512">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="2">
+        <v>46176.32291666666</v>
+      </c>
+      <c r="B513">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="2">
+        <v>46176.33333333334</v>
+      </c>
+      <c r="B514">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="2">
+        <v>46176.34375</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="2">
+        <v>46176.35416666666</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="2">
+        <v>46176.36458333334</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="2">
+        <v>46176.375</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="2">
+        <v>46176.38541666666</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="2">
+        <v>46176.39583333334</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="2">
+        <v>46176.40625</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="2">
+        <v>46176.41666666666</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="2">
+        <v>46176.42708333334</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="2">
+        <v>46176.4375</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="2">
+        <v>46176.44791666666</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="2">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="2">
+        <v>46176.46875</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="2">
+        <v>46176.47916666666</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="2">
+        <v>46176.48958333334</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="2">
+        <v>46176.5</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="2">
+        <v>46176.51041666666</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="2">
+        <v>46176.52083333334</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="2">
+        <v>46176.53125</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="2">
+        <v>46176.54166666666</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="2">
+        <v>46176.55208333334</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="2">
+        <v>46176.5625</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="2">
+        <v>46176.57291666666</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="2">
+        <v>46176.58333333334</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="2">
+        <v>46176.59375</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="2">
+        <v>46176.60416666666</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="2">
+        <v>46176.61458333334</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="2">
+        <v>46176.625</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="2">
+        <v>46176.63541666666</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="2">
+        <v>46176.64583333334</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="2">
+        <v>46176.65625</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="2">
+        <v>46176.66666666666</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="2">
+        <v>46176.67708333334</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="2">
+        <v>46176.6875</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="2">
+        <v>46176.69791666666</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="2">
+        <v>46176.70833333334</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="2">
+        <v>46176.71875</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="2">
+        <v>46176.72916666666</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="2">
+        <v>46176.73958333334</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="2">
+        <v>46176.75</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="2">
+        <v>46176.76041666666</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="2">
+        <v>46176.77083333334</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="2">
+        <v>46176.78125</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="2">
+        <v>46176.79166666666</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="2">
+        <v>46176.80208333334</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="2">
+        <v>46176.8125</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="2">
+        <v>46176.82291666666</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="2">
+        <v>46176.83333333334</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="2">
+        <v>46176.84375</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="2">
+        <v>46176.85416666666</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="2">
+        <v>46176.86458333334</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="2">
+        <v>46176.875</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="2">
+        <v>46176.88541666666</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="2">
+        <v>46176.89583333334</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="2">
+        <v>46176.90625</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="2">
+        <v>46176.91666666666</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="2">
+        <v>46176.92708333334</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="2">
+        <v>46176.9375</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="2">
+        <v>46176.94791666666</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="2">
+        <v>46176.95833333334</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="2">
+        <v>46176.96875</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="2">
+        <v>46176.97916666666</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="2">
+        <v>46176.98958333334</v>
+      </c>
+      <c r="B577">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46185.03125</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46185.0625</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46185.09375</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46185.125</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46185.15625</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46185.1875</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,495 +546,495 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46185.21875</v>
       </c>
       <c r="B22">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B23">
-        <v>92</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B24">
-        <v>159</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46185.25</v>
       </c>
       <c r="B25">
-        <v>247</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B26">
-        <v>361</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B27">
-        <v>494</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46185.28125</v>
       </c>
       <c r="B28">
-        <v>641</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B29">
-        <v>771</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B30">
-        <v>948</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46185.3125</v>
       </c>
       <c r="B31">
-        <v>1093</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B32">
-        <v>1270</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B33">
-        <v>1432</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46185.34375</v>
       </c>
       <c r="B34">
-        <v>1574</v>
+        <v>531</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B35">
-        <v>1661</v>
+        <v>593</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B36">
-        <v>1764</v>
+        <v>708</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46185.375</v>
       </c>
       <c r="B37">
-        <v>1868</v>
+        <v>816</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B38">
-        <v>1949</v>
+        <v>901</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B39">
-        <v>2047</v>
+        <v>939</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46185.40625</v>
       </c>
       <c r="B40">
-        <v>2138</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B41">
-        <v>2190</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B42">
-        <v>2272</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46185.4375</v>
       </c>
       <c r="B43">
-        <v>2376</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B44">
-        <v>2403</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B45">
-        <v>2431</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46185.46875</v>
       </c>
       <c r="B46">
-        <v>2374</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B47">
-        <v>2361</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B48">
-        <v>2371</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46185.5</v>
       </c>
       <c r="B49">
-        <v>2415</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B50">
-        <v>2407</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B51">
-        <v>2413</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46185.53125</v>
       </c>
       <c r="B52">
-        <v>2398</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B54">
-        <v>2294</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46185.5625</v>
       </c>
       <c r="B55">
-        <v>2252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B56">
-        <v>2222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B57">
-        <v>2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46185.59375</v>
       </c>
       <c r="B58">
-        <v>2139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B59">
-        <v>2099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B60">
-        <v>2053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46185.625</v>
       </c>
       <c r="B61">
-        <v>1983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B62">
-        <v>1932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B63">
-        <v>1846</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46185.65625</v>
       </c>
       <c r="B64">
-        <v>1790</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B65">
-        <v>1665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B66">
-        <v>1601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46185.6875</v>
       </c>
       <c r="B67">
-        <v>1568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B68">
-        <v>1518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B69">
-        <v>1369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46185.71875</v>
       </c>
       <c r="B70">
-        <v>1156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B71">
-        <v>967</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B72">
-        <v>843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46185.75</v>
       </c>
       <c r="B73">
-        <v>686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B74">
-        <v>556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B75">
-        <v>424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46185.78125</v>
       </c>
       <c r="B76">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B77">
-        <v>233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B78">
-        <v>141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46185.8125</v>
       </c>
       <c r="B79">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B80">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B81">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46185.84375</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46185.875</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46185.90625</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46185.9375</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46185.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,777 +1154,9 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46186</v>
       </c>
       <c r="B97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="2">
-        <v>46177</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="2">
-        <v>46177.01041666666</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="2">
-        <v>46177.02083333334</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="2">
-        <v>46177.03125</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="2">
-        <v>46177.04166666666</v>
-      </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="2">
-        <v>46177.05208333334</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="2">
-        <v>46177.0625</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="2">
-        <v>46177.07291666666</v>
-      </c>
-      <c r="B105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="2">
-        <v>46177.08333333334</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="2">
-        <v>46177.09375</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="2">
-        <v>46177.10416666666</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="2">
-        <v>46177.11458333334</v>
-      </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="2">
-        <v>46177.125</v>
-      </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="2">
-        <v>46177.13541666666</v>
-      </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="2">
-        <v>46177.14583333334</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="2">
-        <v>46177.15625</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="2">
-        <v>46177.16666666666</v>
-      </c>
-      <c r="B114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="2">
-        <v>46177.17708333334</v>
-      </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="2">
-        <v>46177.1875</v>
-      </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="2">
-        <v>46177.19791666666</v>
-      </c>
-      <c r="B117">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="2">
-        <v>46177.20833333334</v>
-      </c>
-      <c r="B118">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="2">
-        <v>46177.21875</v>
-      </c>
-      <c r="B119">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="2">
-        <v>46177.22916666666</v>
-      </c>
-      <c r="B120">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="2">
-        <v>46177.23958333334</v>
-      </c>
-      <c r="B121">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="2">
-        <v>46177.25</v>
-      </c>
-      <c r="B122">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="2">
-        <v>46177.26041666666</v>
-      </c>
-      <c r="B123">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="2">
-        <v>46177.27083333334</v>
-      </c>
-      <c r="B124">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="2">
-        <v>46177.28125</v>
-      </c>
-      <c r="B125">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="2">
-        <v>46177.29166666666</v>
-      </c>
-      <c r="B126">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="2">
-        <v>46177.30208333334</v>
-      </c>
-      <c r="B127">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="2">
-        <v>46177.3125</v>
-      </c>
-      <c r="B128">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="2">
-        <v>46177.32291666666</v>
-      </c>
-      <c r="B129">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="2">
-        <v>46177.33333333334</v>
-      </c>
-      <c r="B130">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="2">
-        <v>46177.34375</v>
-      </c>
-      <c r="B131">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="2">
-        <v>46177.35416666666</v>
-      </c>
-      <c r="B132">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="2">
-        <v>46177.36458333334</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="2">
-        <v>46177.375</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="2">
-        <v>46177.38541666666</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="2">
-        <v>46177.39583333334</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="2">
-        <v>46177.40625</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="2">
-        <v>46177.41666666666</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="2">
-        <v>46177.42708333334</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="2">
-        <v>46177.4375</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="2">
-        <v>46177.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="2">
-        <v>46177.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="2">
-        <v>46177.46875</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2">
-        <v>46177.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="2">
-        <v>46177.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="2">
-        <v>46177.5</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="2">
-        <v>46177.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="2">
-        <v>46177.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="2">
-        <v>46177.53125</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="2">
-        <v>46177.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="2">
-        <v>46177.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2">
-        <v>46177.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2">
-        <v>46177.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2">
-        <v>46177.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2">
-        <v>46177.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2">
-        <v>46177.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2">
-        <v>46177.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2">
-        <v>46177.625</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2">
-        <v>46177.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2">
-        <v>46177.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2">
-        <v>46177.65625</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2">
-        <v>46177.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2">
-        <v>46177.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2">
-        <v>46177.6875</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2">
-        <v>46177.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2">
-        <v>46177.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2">
-        <v>46177.71875</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2">
-        <v>46177.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2">
-        <v>46177.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2">
-        <v>46177.75</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2">
-        <v>46177.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2">
-        <v>46177.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2">
-        <v>46177.78125</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2">
-        <v>46177.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="2">
-        <v>46177.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2">
-        <v>46177.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2">
-        <v>46177.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2">
-        <v>46177.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2">
-        <v>46177.84375</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2">
-        <v>46177.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2">
-        <v>46177.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2">
-        <v>46177.875</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2">
-        <v>46177.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46177.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46177.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46177.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46177.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46177.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46177.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="2">
-        <v>46177.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2">
-        <v>46177.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2">
-        <v>46177.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2">
-        <v>46177.98958333334</v>
-      </c>
-      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46185.01041666666</v>
+        <v>46213</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46185.03125</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46185.0625</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46185.09375</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46185.125</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46185.15625</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46185.1875</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,618 +546,210 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46185.21875</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B24">
-        <v>35</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46185.25</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B25">
-        <v>51</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>78</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B27">
-        <v>117</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46185.28125</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B28">
-        <v>162</v>
+        <v>612</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>217</v>
+        <v>780</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B30">
-        <v>274</v>
+        <v>967</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46185.3125</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B31">
-        <v>340</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>410</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B33">
-        <v>458</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46185.34375</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B34">
-        <v>531</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>593</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B36">
-        <v>708</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46185.375</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B37">
-        <v>816</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>901</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B39">
-        <v>939</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46185.40625</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B40">
-        <v>1053</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
-        <v>1041</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B42">
-        <v>1077</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46185.4375</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B43">
-        <v>1079</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>1085</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46185.45833333334</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B45">
-        <v>1181</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46185.46875</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B46">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2">
-        <v>46185.47916666666</v>
-      </c>
-      <c r="B47">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2">
-        <v>46185.48958333334</v>
-      </c>
-      <c r="B48">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2">
-        <v>46185.5</v>
-      </c>
-      <c r="B49">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2">
-        <v>46185.51041666666</v>
-      </c>
-      <c r="B50">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2">
-        <v>46185.52083333334</v>
-      </c>
-      <c r="B51">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="2">
-        <v>46185.53125</v>
-      </c>
-      <c r="B52">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2">
-        <v>46185.54166666666</v>
-      </c>
-      <c r="B53">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="2">
-        <v>46185.55208333334</v>
-      </c>
-      <c r="B54">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="2">
-        <v>46185.5625</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="2">
-        <v>46185.57291666666</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="2">
-        <v>46185.58333333334</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="2">
-        <v>46185.59375</v>
-      </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="2">
-        <v>46185.60416666666</v>
-      </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="2">
-        <v>46185.61458333334</v>
-      </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="2">
-        <v>46185.625</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="2">
-        <v>46185.63541666666</v>
-      </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="2">
-        <v>46185.64583333334</v>
-      </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="2">
-        <v>46185.65625</v>
-      </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="2">
-        <v>46185.66666666666</v>
-      </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="2">
-        <v>46185.67708333334</v>
-      </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="2">
-        <v>46185.6875</v>
-      </c>
-      <c r="B67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="2">
-        <v>46185.69791666666</v>
-      </c>
-      <c r="B68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="2">
-        <v>46185.70833333334</v>
-      </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="2">
-        <v>46185.71875</v>
-      </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="2">
-        <v>46185.72916666666</v>
-      </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="2">
-        <v>46185.73958333334</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="2">
-        <v>46185.75</v>
-      </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="2">
-        <v>46185.76041666666</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="2">
-        <v>46185.77083333334</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="2">
-        <v>46185.78125</v>
-      </c>
-      <c r="B76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="2">
-        <v>46185.79166666666</v>
-      </c>
-      <c r="B77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="2">
-        <v>46185.80208333334</v>
-      </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="2">
-        <v>46185.8125</v>
-      </c>
-      <c r="B79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="2">
-        <v>46185.82291666666</v>
-      </c>
-      <c r="B80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="2">
-        <v>46185.83333333334</v>
-      </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="2">
-        <v>46185.84375</v>
-      </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="2">
-        <v>46185.85416666666</v>
-      </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="2">
-        <v>46185.86458333334</v>
-      </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="2">
-        <v>46185.875</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="2">
-        <v>46185.88541666666</v>
-      </c>
-      <c r="B86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="2">
-        <v>46185.89583333334</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="2">
-        <v>46185.90625</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="2">
-        <v>46185.91666666666</v>
-      </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="2">
-        <v>46185.92708333334</v>
-      </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="2">
-        <v>46185.9375</v>
-      </c>
-      <c r="B91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="2">
-        <v>46185.94791666666</v>
-      </c>
-      <c r="B92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="2">
-        <v>46185.95833333334</v>
-      </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B97">
-        <v>0</v>
+        <v>2612</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46213.01041666666</v>
+        <v>46216.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46213.02083333334</v>
+        <v>46216.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46213.03125</v>
+        <v>46216.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46213.04166666666</v>
+        <v>46216.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46213.05208333334</v>
+        <v>46216.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46213.0625</v>
+        <v>46216.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46213.07291666666</v>
+        <v>46216.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46213.08333333334</v>
+        <v>46216.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46213.09375</v>
+        <v>46216.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46213.10416666666</v>
+        <v>46216.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46213.11458333334</v>
+        <v>46216.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46213.125</v>
+        <v>46216.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46213.13541666666</v>
+        <v>46216.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46213.14583333334</v>
+        <v>46216.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46213.15625</v>
+        <v>46216.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46213.16666666666</v>
+        <v>46216.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46213.17708333334</v>
+        <v>46216.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46213.1875</v>
+        <v>46216.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46213.19791666666</v>
+        <v>46216.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,202 +554,258 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46213.20833333334</v>
+        <v>46216.20833333334</v>
       </c>
       <c r="B22">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46213.21875</v>
+        <v>46216.21875</v>
       </c>
       <c r="B23">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46213.22916666666</v>
+        <v>46216.22916666666</v>
       </c>
       <c r="B24">
-        <v>141</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46213.23958333334</v>
+        <v>46216.23958333334</v>
       </c>
       <c r="B25">
-        <v>217</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46213.25</v>
+        <v>46216.25</v>
       </c>
       <c r="B26">
-        <v>317</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46213.26041666666</v>
+        <v>46216.26041666666</v>
       </c>
       <c r="B27">
-        <v>463</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46213.27083333334</v>
+        <v>46216.27083333334</v>
       </c>
       <c r="B28">
-        <v>612</v>
+        <v>549</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46213.28125</v>
+        <v>46216.28125</v>
       </c>
       <c r="B29">
-        <v>780</v>
+        <v>692</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46213.29166666666</v>
+        <v>46216.29166666666</v>
       </c>
       <c r="B30">
-        <v>967</v>
+        <v>913</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46213.30208333334</v>
+        <v>46216.30208333334</v>
       </c>
       <c r="B31">
-        <v>1231</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46213.3125</v>
+        <v>46216.3125</v>
       </c>
       <c r="B32">
-        <v>1495</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46213.32291666666</v>
+        <v>46216.32291666666</v>
       </c>
       <c r="B33">
-        <v>1613</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46213.33333333334</v>
+        <v>46216.33333333334</v>
       </c>
       <c r="B34">
-        <v>1749</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46213.34375</v>
+        <v>46216.34375</v>
       </c>
       <c r="B35">
-        <v>1883</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46213.35416666666</v>
+        <v>46216.35416666666</v>
       </c>
       <c r="B36">
-        <v>1870</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46213.36458333334</v>
+        <v>46216.36458333334</v>
       </c>
       <c r="B37">
-        <v>2024</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46213.375</v>
+        <v>46216.375</v>
       </c>
       <c r="B38">
-        <v>2209</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46213.38541666666</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="B39">
-        <v>2369</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46213.39583333334</v>
+        <v>46216.39583333334</v>
       </c>
       <c r="B40">
-        <v>2340</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46213.40625</v>
+        <v>46216.40625</v>
       </c>
       <c r="B41">
-        <v>2420</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46213.41666666666</v>
+        <v>46216.41666666666</v>
       </c>
       <c r="B42">
-        <v>2475</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46213.42708333334</v>
+        <v>46216.42708333334</v>
       </c>
       <c r="B43">
-        <v>2589</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46213.4375</v>
+        <v>46216.4375</v>
       </c>
       <c r="B44">
-        <v>2589</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46213.44791666666</v>
+        <v>46216.44791666666</v>
       </c>
       <c r="B45">
-        <v>2576</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46213.45833333334</v>
+        <v>46216.45833333334</v>
       </c>
       <c r="B46">
-        <v>2612</v>
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46216.46875</v>
+      </c>
+      <c r="B47">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46216.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46216.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46216.5</v>
+      </c>
+      <c r="B50">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46216.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
+        <v>46216.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
+        <v>46216.53125</v>
+      </c>
+      <c r="B53">
+        <v>1872</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46216.01041666666</v>
+        <v>46218.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46216.02083333334</v>
+        <v>46218.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46216.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46216.04166666666</v>
+        <v>46218.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46216.05208333334</v>
+        <v>46218.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46216.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46216.07291666666</v>
+        <v>46218.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46216.08333333334</v>
+        <v>46218.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46216.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46216.10416666666</v>
+        <v>46218.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46216.11458333334</v>
+        <v>46218.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46216.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46216.13541666666</v>
+        <v>46218.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46216.14583333334</v>
+        <v>46218.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46216.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46216.16666666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46216.17708333334</v>
+        <v>46218.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46216.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46216.19791666666</v>
+        <v>46218.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,258 +554,202 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46216.20833333334</v>
+        <v>46218.20833333334</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46216.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46216.22916666666</v>
+        <v>46218.22916666666</v>
       </c>
       <c r="B24">
-        <v>103</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46216.23958333334</v>
+        <v>46218.23958333334</v>
       </c>
       <c r="B25">
-        <v>167</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46216.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>264</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46216.26041666666</v>
+        <v>46218.26041666666</v>
       </c>
       <c r="B27">
-        <v>405</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46216.27083333334</v>
+        <v>46218.27083333334</v>
       </c>
       <c r="B28">
-        <v>549</v>
+        <v>659</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46216.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>692</v>
+        <v>833</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46216.29166666666</v>
+        <v>46218.29166666666</v>
       </c>
       <c r="B30">
-        <v>913</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46216.30208333334</v>
+        <v>46218.30208333334</v>
       </c>
       <c r="B31">
-        <v>1046</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46216.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>1199</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46216.32291666666</v>
+        <v>46218.32291666666</v>
       </c>
       <c r="B33">
-        <v>1448</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46216.33333333334</v>
+        <v>46218.33333333334</v>
       </c>
       <c r="B34">
-        <v>1492</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46216.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>1549</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46216.35416666666</v>
+        <v>46218.35416666666</v>
       </c>
       <c r="B36">
-        <v>1709</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46216.36458333334</v>
+        <v>46218.36458333334</v>
       </c>
       <c r="B37">
-        <v>1653</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46216.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>1799</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46216.38541666666</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="B39">
-        <v>1921</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46216.39583333334</v>
+        <v>46218.39583333334</v>
       </c>
       <c r="B40">
-        <v>1813</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46216.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
-        <v>1998</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46216.41666666666</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="B42">
-        <v>2039</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46216.42708333334</v>
+        <v>46218.42708333334</v>
       </c>
       <c r="B43">
-        <v>1977</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46216.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
-        <v>1982</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46216.44791666666</v>
+        <v>46218.44791666666</v>
       </c>
       <c r="B45">
-        <v>1952</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46216.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="B46">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2">
-        <v>46216.46875</v>
-      </c>
-      <c r="B47">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2">
-        <v>46216.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2">
-        <v>46216.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2">
-        <v>46216.5</v>
-      </c>
-      <c r="B50">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2">
-        <v>46216.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="2">
-        <v>46216.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2">
-        <v>46216.53125</v>
-      </c>
-      <c r="B53">
-        <v>1872</v>
+        <v>2579</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2977832ADC31921FD2FE31D2F8375B06A41B6E9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00155445-E2DE-4368-A107-11FA47E47291}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,364 +425,348 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46218.01041666666</v>
+        <v>46219.010416666657</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46218.02083333334</v>
+        <v>46219.020833333343</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46218.04166666666</v>
+        <v>46219.041666666657</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46218.05208333334</v>
+        <v>46219.052083333343</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46218.07291666666</v>
+        <v>46219.072916666657</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46218.08333333334</v>
+        <v>46219.083333333343</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46218.10416666666</v>
+        <v>46219.104166666657</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46218.11458333334</v>
+        <v>46219.114583333343</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46218.13541666666</v>
+        <v>46219.135416666657</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46218.14583333334</v>
+        <v>46219.145833333343</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46218.16666666666</v>
+        <v>46219.166666666657</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46218.17708333334</v>
+        <v>46219.177083333343</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46218.19791666666</v>
+        <v>46219.197916666657</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46218.20833333334</v>
+        <v>46219.208333333343</v>
       </c>
       <c r="B22">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B23">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46218.22916666666</v>
+        <v>46219.229166666657</v>
       </c>
       <c r="B24">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46218.23958333334</v>
+        <v>46219.239583333343</v>
       </c>
       <c r="B25">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B26">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46218.26041666666</v>
+        <v>46219.260416666657</v>
       </c>
       <c r="B27">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46218.27083333334</v>
+        <v>46219.270833333343</v>
       </c>
       <c r="B28">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46218.28125</v>
+        <v>46219.28125</v>
       </c>
       <c r="B29">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46218.29166666666</v>
+        <v>46219.291666666657</v>
       </c>
       <c r="B30">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46218.30208333334</v>
+        <v>46219.302083333343</v>
       </c>
       <c r="B31">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46218.3125</v>
+        <v>46219.3125</v>
       </c>
       <c r="B32">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46219.322916666657</v>
+      </c>
+      <c r="B33">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46219.333333333343</v>
+      </c>
+      <c r="B34">
         <v>1397</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="2">
-        <v>46218.32291666666</v>
-      </c>
-      <c r="B33">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="2">
-        <v>46218.33333333334</v>
-      </c>
-      <c r="B34">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46218.34375</v>
+        <v>46219.34375</v>
       </c>
       <c r="B35">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46218.35416666666</v>
+        <v>46219.354166666657</v>
       </c>
       <c r="B36">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46218.36458333334</v>
+        <v>46219.364583333343</v>
       </c>
       <c r="B37">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46218.375</v>
+        <v>46219.375</v>
       </c>
       <c r="B38">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46218.38541666666</v>
+        <v>46219.385416666657</v>
       </c>
       <c r="B39">
-        <v>2272</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46218.39583333334</v>
+        <v>46219.395833333343</v>
       </c>
       <c r="B40">
-        <v>2367</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B41">
-        <v>2437</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46218.41666666666</v>
+        <v>46219.416666666657</v>
       </c>
       <c r="B42">
-        <v>2479</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46218.42708333334</v>
+        <v>46219.427083333343</v>
       </c>
       <c r="B43">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46218.4375</v>
+        <v>46219.4375</v>
       </c>
       <c r="B44">
-        <v>2576</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2">
-        <v>46218.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>2596</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2">
-        <v>46218.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>2579</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2977832ADC31921FD2FE31D2F8375B06A41B6E9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00155445-E2DE-4368-A107-11FA47E47291}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,348 +392,252 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46219.010416666657</v>
+        <v>46223.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46219.020833333343</v>
+        <v>46223.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46219.03125</v>
+        <v>46223.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46219.041666666657</v>
+        <v>46223.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46219.052083333343</v>
+        <v>46223.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46219.0625</v>
+        <v>46223.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46219.072916666657</v>
+        <v>46223.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46219.083333333343</v>
+        <v>46223.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46219.09375</v>
+        <v>46223.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46219.104166666657</v>
+        <v>46223.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46219.114583333343</v>
+        <v>46223.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46219.125</v>
+        <v>46223.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46219.135416666657</v>
+        <v>46223.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46219.145833333343</v>
+        <v>46223.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46219.15625</v>
+        <v>46223.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46219.166666666657</v>
+        <v>46223.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46219.177083333343</v>
+        <v>46223.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46219.1875</v>
+        <v>46223.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46219.197916666657</v>
+        <v>46223.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46219.208333333343</v>
+        <v>46223.20833333334</v>
       </c>
       <c r="B22">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46219.21875</v>
+        <v>46223.21875</v>
       </c>
       <c r="B23">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46219.229166666657</v>
+        <v>46223.22916666666</v>
       </c>
       <c r="B24">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46219.239583333343</v>
+        <v>46223.23958333334</v>
       </c>
       <c r="B25">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46219.25</v>
+        <v>46223.25</v>
       </c>
       <c r="B26">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46219.260416666657</v>
+        <v>46223.26041666666</v>
       </c>
       <c r="B27">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46219.270833333343</v>
+        <v>46223.27083333334</v>
       </c>
       <c r="B28">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46219.28125</v>
+        <v>46223.28125</v>
       </c>
       <c r="B29">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46219.291666666657</v>
+        <v>46223.29166666666</v>
       </c>
       <c r="B30">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46219.302083333343</v>
+        <v>46223.30208333334</v>
       </c>
       <c r="B31">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46219.3125</v>
+        <v>46223.3125</v>
       </c>
       <c r="B32">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>46219.322916666657</v>
-      </c>
-      <c r="B33">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>46219.333333333343</v>
-      </c>
-      <c r="B34">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>46219.34375</v>
-      </c>
-      <c r="B35">
-        <v>1502</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>46219.354166666657</v>
-      </c>
-      <c r="B36">
-        <v>1609</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>46219.364583333343</v>
-      </c>
-      <c r="B37">
-        <v>1762</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>46219.375</v>
-      </c>
-      <c r="B38">
-        <v>1829</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>46219.385416666657</v>
-      </c>
-      <c r="B39">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>46219.395833333343</v>
-      </c>
-      <c r="B40">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>46219.40625</v>
-      </c>
-      <c r="B41">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>46219.416666666657</v>
-      </c>
-      <c r="B42">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>46219.427083333343</v>
-      </c>
-      <c r="B43">
-        <v>2293</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>46219.4375</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46223.01041666666</v>
+        <v>46226.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46223.02083333334</v>
+        <v>46226.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46223.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46223.04166666666</v>
+        <v>46226.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46223.05208333334</v>
+        <v>46226.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46223.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46223.07291666666</v>
+        <v>46226.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46223.08333333334</v>
+        <v>46226.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46223.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46223.10416666666</v>
+        <v>46226.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46223.11458333334</v>
+        <v>46226.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46223.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46223.13541666666</v>
+        <v>46226.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46223.14583333334</v>
+        <v>46226.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46223.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46223.16666666666</v>
+        <v>46226.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46223.17708333334</v>
+        <v>46226.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46223.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46223.19791666666</v>
+        <v>46226.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,90 +554,82 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46223.20833333334</v>
+        <v>46226.20833333334</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46223.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46223.22916666666</v>
+        <v>46226.22916666666</v>
       </c>
       <c r="B24">
-        <v>99</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46223.23958333334</v>
+        <v>46226.23958333334</v>
       </c>
       <c r="B25">
-        <v>161</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46223.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46223.26041666666</v>
+        <v>46226.26041666666</v>
       </c>
       <c r="B27">
-        <v>294</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46223.27083333334</v>
+        <v>46226.27083333334</v>
       </c>
       <c r="B28">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46223.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>517</v>
+        <v>623</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46223.29166666666</v>
+        <v>46226.29166666666</v>
       </c>
       <c r="B30">
-        <v>632</v>
+        <v>805</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46223.30208333334</v>
+        <v>46226.30208333334</v>
       </c>
       <c r="B31">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="2">
-        <v>46223.3125</v>
-      </c>
-      <c r="B32">
-        <v>949</v>
+        <v>996</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46226.01041666666</v>
+        <v>46227.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46226.02083333334</v>
+        <v>46227.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46226.04166666666</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46226.05208333334</v>
+        <v>46227.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46226.07291666666</v>
+        <v>46227.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46226.08333333334</v>
+        <v>46227.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46226.10416666666</v>
+        <v>46227.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46226.11458333334</v>
+        <v>46227.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46226.13541666666</v>
+        <v>46227.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46226.14583333334</v>
+        <v>46227.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46226.16666666666</v>
+        <v>46227.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46226.17708333334</v>
+        <v>46227.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46226.19791666666</v>
+        <v>46227.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,82 +554,90 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46226.20833333334</v>
+        <v>46227.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
       <c r="B23">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46226.22916666666</v>
+        <v>46227.22916666666</v>
       </c>
       <c r="B24">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46226.23958333334</v>
+        <v>46227.23958333334</v>
       </c>
       <c r="B25">
-        <v>140</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
       <c r="B26">
-        <v>239</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46226.26041666666</v>
+        <v>46227.26041666666</v>
       </c>
       <c r="B27">
-        <v>327</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46226.27083333334</v>
+        <v>46227.27083333334</v>
       </c>
       <c r="B28">
-        <v>439</v>
+        <v>579</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
       <c r="B29">
-        <v>623</v>
+        <v>728</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46226.29166666666</v>
+        <v>46227.29166666666</v>
       </c>
       <c r="B30">
-        <v>805</v>
+        <v>917</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46226.30208333334</v>
+        <v>46227.30208333334</v>
       </c>
       <c r="B31">
-        <v>996</v>
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2">
+        <v>46227.3125</v>
+      </c>
+      <c r="B32">
+        <v>1350</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46227.01041666666</v>
+        <v>46229.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46227.02083333334</v>
+        <v>46229.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46227.04166666666</v>
+        <v>46229.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46227.05208333334</v>
+        <v>46229.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46227.07291666666</v>
+        <v>46229.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46227.08333333334</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46227.10416666666</v>
+        <v>46229.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46227.11458333334</v>
+        <v>46229.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46227.13541666666</v>
+        <v>46229.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46227.14583333334</v>
+        <v>46229.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46227.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46227.17708333334</v>
+        <v>46229.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46227.19791666666</v>
+        <v>46229.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,90 +554,98 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46227.20833333334</v>
+        <v>46229.20833333334</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
       <c r="B23">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46227.22916666666</v>
+        <v>46229.22916666666</v>
       </c>
       <c r="B24">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46227.23958333334</v>
+        <v>46229.23958333334</v>
       </c>
       <c r="B25">
-        <v>192</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
       <c r="B26">
-        <v>297</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46227.26041666666</v>
+        <v>46229.26041666666</v>
       </c>
       <c r="B27">
-        <v>441</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46227.27083333334</v>
+        <v>46229.27083333334</v>
       </c>
       <c r="B28">
-        <v>579</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
       <c r="B29">
-        <v>728</v>
+        <v>647</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46227.29166666666</v>
+        <v>46229.29166666666</v>
       </c>
       <c r="B30">
-        <v>917</v>
+        <v>813</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46227.30208333334</v>
+        <v>46229.30208333334</v>
       </c>
       <c r="B31">
-        <v>1155</v>
+        <v>986</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
       </c>
       <c r="B32">
-        <v>1350</v>
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2">
+        <v>46229.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>1285</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46229.01041666666</v>
+        <v>46246.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46229.02083333334</v>
+        <v>46246.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46229.04166666666</v>
+        <v>46246.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46229.05208333334</v>
+        <v>46246.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46229.07291666666</v>
+        <v>46246.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46229.08333333334</v>
+        <v>46246.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46229.10416666666</v>
+        <v>46246.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46229.11458333334</v>
+        <v>46246.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46229.13541666666</v>
+        <v>46246.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46229.14583333334</v>
+        <v>46246.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46229.16666666666</v>
+        <v>46246.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46229.17708333334</v>
+        <v>46246.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46229.19791666666</v>
+        <v>46246.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46229.20833333334</v>
+        <v>46246.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,90 +562,274 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46229.22916666666</v>
+        <v>46246.22916666666</v>
       </c>
       <c r="B24">
-        <v>71</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46229.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="B25">
-        <v>139</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
       <c r="B26">
-        <v>233</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46229.26041666666</v>
+        <v>46246.26041666666</v>
       </c>
       <c r="B27">
-        <v>351</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46229.27083333334</v>
+        <v>46246.27083333334</v>
       </c>
       <c r="B28">
-        <v>489</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
       <c r="B29">
-        <v>647</v>
+        <v>602</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46229.29166666666</v>
+        <v>46246.29166666666</v>
       </c>
       <c r="B30">
-        <v>813</v>
+        <v>819</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46229.30208333334</v>
+        <v>46246.30208333334</v>
       </c>
       <c r="B31">
-        <v>986</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
       <c r="B32">
-        <v>1129</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46229.32291666666</v>
+        <v>46246.32291666666</v>
       </c>
       <c r="B33">
-        <v>1285</v>
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2">
+        <v>46246.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2">
+        <v>46246.34375</v>
+      </c>
+      <c r="B35">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2">
+        <v>46246.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46246.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46246.375</v>
+      </c>
+      <c r="B38">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46246.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46246.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46246.40625</v>
+      </c>
+      <c r="B41">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
+        <v>46246.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
+        <v>46246.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
+        <v>46246.4375</v>
+      </c>
+      <c r="B44">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
+        <v>46246.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
+        <v>46246.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46246.46875</v>
+      </c>
+      <c r="B47">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46246.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46246.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46246.5</v>
+      </c>
+      <c r="B50">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46246.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
+        <v>46246.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
+        <v>46246.53125</v>
+      </c>
+      <c r="B53">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2">
+        <v>46246.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2">
+        <v>46246.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2">
+        <v>46246.5625</v>
+      </c>
+      <c r="B56">
+        <v>2916</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46246.01041666666</v>
+        <v>46251.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46246.02083333334</v>
+        <v>46251.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46246.03125</v>
+        <v>46251.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46246.04166666666</v>
+        <v>46251.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46246.05208333334</v>
+        <v>46251.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46246.0625</v>
+        <v>46251.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46246.07291666666</v>
+        <v>46251.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46246.08333333334</v>
+        <v>46251.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46246.09375</v>
+        <v>46251.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46246.10416666666</v>
+        <v>46251.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46246.11458333334</v>
+        <v>46251.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46246.125</v>
+        <v>46251.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46246.13541666666</v>
+        <v>46251.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46246.14583333334</v>
+        <v>46251.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46246.15625</v>
+        <v>46251.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46246.16666666666</v>
+        <v>46251.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46246.17708333334</v>
+        <v>46251.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46246.1875</v>
+        <v>46251.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46246.19791666666</v>
+        <v>46251.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46246.20833333334</v>
+        <v>46251.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46246.21875</v>
+        <v>46251.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,266 +570,98 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46246.22916666666</v>
+        <v>46251.22916666666</v>
       </c>
       <c r="B24">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46246.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="B25">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46246.25</v>
+        <v>46251.25</v>
       </c>
       <c r="B26">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46246.26041666666</v>
+        <v>46251.26041666666</v>
       </c>
       <c r="B27">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46246.27083333334</v>
+        <v>46251.27083333334</v>
       </c>
       <c r="B28">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46246.28125</v>
+        <v>46251.28125</v>
       </c>
       <c r="B29">
-        <v>602</v>
+        <v>647</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46246.29166666666</v>
+        <v>46251.29166666666</v>
       </c>
       <c r="B30">
-        <v>819</v>
+        <v>907</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46246.30208333334</v>
+        <v>46251.30208333334</v>
       </c>
       <c r="B31">
-        <v>1020</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46246.3125</v>
+        <v>46251.3125</v>
       </c>
       <c r="B32">
-        <v>1286</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46246.32291666666</v>
+        <v>46251.32291666666</v>
       </c>
       <c r="B33">
-        <v>1459</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46246.33333333334</v>
+        <v>46251.33333333334</v>
       </c>
       <c r="B34">
-        <v>1668</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46246.34375</v>
+        <v>46251.34375</v>
       </c>
       <c r="B35">
-        <v>1845</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="2">
-        <v>46246.35416666666</v>
-      </c>
-      <c r="B36">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2">
-        <v>46246.36458333334</v>
-      </c>
-      <c r="B37">
-        <v>2092</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="2">
-        <v>46246.375</v>
-      </c>
-      <c r="B38">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2">
-        <v>46246.38541666666</v>
-      </c>
-      <c r="B39">
-        <v>2356</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="2">
-        <v>46246.39583333334</v>
-      </c>
-      <c r="B40">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2">
-        <v>46246.40625</v>
-      </c>
-      <c r="B41">
-        <v>2519</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="2">
-        <v>46246.41666666666</v>
-      </c>
-      <c r="B42">
-        <v>2607</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2">
-        <v>46246.42708333334</v>
-      </c>
-      <c r="B43">
-        <v>2673</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2">
-        <v>46246.4375</v>
-      </c>
-      <c r="B44">
-        <v>2764</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2">
-        <v>46246.44791666666</v>
-      </c>
-      <c r="B45">
-        <v>2810</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2">
-        <v>46246.45833333334</v>
-      </c>
-      <c r="B46">
-        <v>2762</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2">
-        <v>46246.46875</v>
-      </c>
-      <c r="B47">
-        <v>2833</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2">
-        <v>46246.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>2889</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2">
-        <v>46246.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>2899</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2">
-        <v>46246.5</v>
-      </c>
-      <c r="B50">
-        <v>2931</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2">
-        <v>46246.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>2951</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="2">
-        <v>46246.52083333334</v>
-      </c>
-      <c r="B52">
-        <v>2931</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2">
-        <v>46246.53125</v>
-      </c>
-      <c r="B53">
-        <v>2925</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="2">
-        <v>46246.54166666666</v>
-      </c>
-      <c r="B54">
-        <v>2881</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="2">
-        <v>46246.55208333334</v>
-      </c>
-      <c r="B55">
-        <v>2907</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="2">
-        <v>46246.5625</v>
-      </c>
-      <c r="B56">
-        <v>2916</v>
+        <v>2114</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46251.01041666666</v>
+        <v>46252.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46251.02083333334</v>
+        <v>46252.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46251.03125</v>
+        <v>46252.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46251.04166666666</v>
+        <v>46252.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46251.05208333334</v>
+        <v>46252.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46251.0625</v>
+        <v>46252.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46251.07291666666</v>
+        <v>46252.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46251.08333333334</v>
+        <v>46252.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46251.09375</v>
+        <v>46252.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46251.10416666666</v>
+        <v>46252.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46251.11458333334</v>
+        <v>46252.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46251.125</v>
+        <v>46252.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46251.13541666666</v>
+        <v>46252.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46251.14583333334</v>
+        <v>46252.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46251.15625</v>
+        <v>46252.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46251.16666666666</v>
+        <v>46252.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46251.17708333334</v>
+        <v>46252.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46251.1875</v>
+        <v>46252.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46251.19791666666</v>
+        <v>46252.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46251.20833333334</v>
+        <v>46252.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46251.21875</v>
+        <v>46252.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,98 +570,122 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46251.22916666666</v>
+        <v>46252.22916666666</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="B25">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46251.25</v>
+        <v>46252.25</v>
       </c>
       <c r="B26">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46251.26041666666</v>
+        <v>46252.26041666666</v>
       </c>
       <c r="B27">
-        <v>276</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46251.27083333334</v>
+        <v>46252.27083333334</v>
       </c>
       <c r="B28">
-        <v>445</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46251.28125</v>
+        <v>46252.28125</v>
       </c>
       <c r="B29">
-        <v>647</v>
+        <v>490</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46251.29166666666</v>
+        <v>46252.29166666666</v>
       </c>
       <c r="B30">
-        <v>907</v>
+        <v>702</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46251.30208333334</v>
+        <v>46252.30208333334</v>
       </c>
       <c r="B31">
-        <v>1162</v>
+        <v>888</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46251.3125</v>
+        <v>46252.3125</v>
       </c>
       <c r="B32">
-        <v>1389</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46251.32291666666</v>
+        <v>46252.32291666666</v>
       </c>
       <c r="B33">
-        <v>1615</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46251.33333333334</v>
+        <v>46252.33333333334</v>
       </c>
       <c r="B34">
-        <v>1885</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46251.34375</v>
+        <v>46252.34375</v>
       </c>
       <c r="B35">
-        <v>2114</v>
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2">
+        <v>46252.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46252.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46252.375</v>
+      </c>
+      <c r="B38">
+        <v>1999</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46252.01041666666</v>
+        <v>46253.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46252.02083333334</v>
+        <v>46253.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46252.03125</v>
+        <v>46253.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46252.04166666666</v>
+        <v>46253.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46252.05208333334</v>
+        <v>46253.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46252.0625</v>
+        <v>46253.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46252.07291666666</v>
+        <v>46253.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46252.08333333334</v>
+        <v>46253.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46252.09375</v>
+        <v>46253.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46252.10416666666</v>
+        <v>46253.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46252.11458333334</v>
+        <v>46253.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46252.125</v>
+        <v>46253.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46252.13541666666</v>
+        <v>46253.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46252.14583333334</v>
+        <v>46253.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46252.15625</v>
+        <v>46253.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46252.16666666666</v>
+        <v>46253.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46252.17708333334</v>
+        <v>46253.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46252.1875</v>
+        <v>46253.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46252.19791666666</v>
+        <v>46253.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46252.20833333334</v>
+        <v>46253.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46252.21875</v>
+        <v>46253.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,122 +570,866 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46252.22916666666</v>
+        <v>46253.22916666666</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46252.23958333334</v>
+        <v>46253.23958333334</v>
       </c>
       <c r="B25">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46252.25</v>
+        <v>46253.25</v>
       </c>
       <c r="B26">
-        <v>126</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46252.26041666666</v>
+        <v>46253.26041666666</v>
       </c>
       <c r="B27">
-        <v>233</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46252.27083333334</v>
+        <v>46253.27083333334</v>
       </c>
       <c r="B28">
-        <v>348</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46252.28125</v>
+        <v>46253.28125</v>
       </c>
       <c r="B29">
-        <v>490</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46252.29166666666</v>
+        <v>46253.29166666666</v>
       </c>
       <c r="B30">
-        <v>702</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46252.30208333334</v>
+        <v>46253.30208333334</v>
       </c>
       <c r="B31">
-        <v>888</v>
+        <v>582</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46252.3125</v>
+        <v>46253.3125</v>
       </c>
       <c r="B32">
-        <v>1103</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46252.32291666666</v>
+        <v>46253.32291666666</v>
       </c>
       <c r="B33">
-        <v>1284</v>
+        <v>969</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46252.33333333334</v>
+        <v>46253.33333333334</v>
       </c>
       <c r="B34">
-        <v>1512</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46252.34375</v>
+        <v>46253.34375</v>
       </c>
       <c r="B35">
-        <v>1649</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46252.35416666666</v>
+        <v>46253.35416666666</v>
       </c>
       <c r="B36">
-        <v>1736</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46252.36458333334</v>
+        <v>46253.36458333334</v>
       </c>
       <c r="B37">
-        <v>1815</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46252.375</v>
+        <v>46253.375</v>
       </c>
       <c r="B38">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46253.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46253.39583333334</v>
+      </c>
+      <c r="B40">
         <v>1999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46253.40625</v>
+      </c>
+      <c r="B41">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
+        <v>46253.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
+        <v>46253.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
+        <v>46253.4375</v>
+      </c>
+      <c r="B44">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
+        <v>46253.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
+        <v>46253.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46253.46875</v>
+      </c>
+      <c r="B47">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46253.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46253.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46253.5</v>
+      </c>
+      <c r="B50">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46253.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2">
+        <v>46253.52083333334</v>
+      </c>
+      <c r="B52">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2">
+        <v>46253.53125</v>
+      </c>
+      <c r="B53">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2">
+        <v>46253.54166666666</v>
+      </c>
+      <c r="B54">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2">
+        <v>46253.55208333334</v>
+      </c>
+      <c r="B55">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2">
+        <v>46253.5625</v>
+      </c>
+      <c r="B56">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2">
+        <v>46253.57291666666</v>
+      </c>
+      <c r="B57">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2">
+        <v>46253.58333333334</v>
+      </c>
+      <c r="B58">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2">
+        <v>46253.59375</v>
+      </c>
+      <c r="B59">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2">
+        <v>46253.60416666666</v>
+      </c>
+      <c r="B60">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2">
+        <v>46253.61458333334</v>
+      </c>
+      <c r="B61">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2">
+        <v>46253.625</v>
+      </c>
+      <c r="B62">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2">
+        <v>46253.63541666666</v>
+      </c>
+      <c r="B63">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2">
+        <v>46253.64583333334</v>
+      </c>
+      <c r="B64">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2">
+        <v>46253.65625</v>
+      </c>
+      <c r="B65">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2">
+        <v>46253.66666666666</v>
+      </c>
+      <c r="B66">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2">
+        <v>46253.67708333334</v>
+      </c>
+      <c r="B67">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2">
+        <v>46253.6875</v>
+      </c>
+      <c r="B68">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2">
+        <v>46253.69791666666</v>
+      </c>
+      <c r="B69">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="2">
+        <v>46253.70833333334</v>
+      </c>
+      <c r="B70">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="2">
+        <v>46253.71875</v>
+      </c>
+      <c r="B71">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2">
+        <v>46253.72916666666</v>
+      </c>
+      <c r="B72">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="2">
+        <v>46253.73958333334</v>
+      </c>
+      <c r="B73">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2">
+        <v>46253.75</v>
+      </c>
+      <c r="B74">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2">
+        <v>46253.76041666666</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2">
+        <v>46253.77083333334</v>
+      </c>
+      <c r="B76">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2">
+        <v>46253.78125</v>
+      </c>
+      <c r="B77">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2">
+        <v>46253.79166666666</v>
+      </c>
+      <c r="B78">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2">
+        <v>46253.80208333334</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2">
+        <v>46253.8125</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2">
+        <v>46253.82291666666</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2">
+        <v>46253.83333333334</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2">
+        <v>46253.84375</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2">
+        <v>46253.85416666666</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2">
+        <v>46253.86458333334</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2">
+        <v>46253.875</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2">
+        <v>46253.88541666666</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2">
+        <v>46253.89583333334</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2">
+        <v>46253.90625</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="2">
+        <v>46253.91666666666</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="2">
+        <v>46253.92708333334</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46253.9375</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46253.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46253.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46253.96875</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46253.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46253.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46254.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46254.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46254.03125</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46254.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46254.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46254.0625</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46254.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46254.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46254.09375</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46254.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46254.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46254.125</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46254.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46254.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46254.15625</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46254.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46254.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46254.1875</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46254.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46254.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46254.21875</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46254.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46254.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46254.25</v>
+      </c>
+      <c r="B122">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46254.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46254.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46254.28125</v>
+      </c>
+      <c r="B125">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46254.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46254.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46254.3125</v>
+      </c>
+      <c r="B128">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46254.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46254.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46254.34375</v>
+      </c>
+      <c r="B131">
+        <v>2146</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46259.01041666666</v>
+        <v>46262.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46259.02083333334</v>
+        <v>46262.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46259.03125</v>
+        <v>46262.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46259.04166666666</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46259.05208333334</v>
+        <v>46262.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46259.0625</v>
+        <v>46262.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46259.07291666666</v>
+        <v>46262.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46259.08333333334</v>
+        <v>46262.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46259.09375</v>
+        <v>46262.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46259.10416666666</v>
+        <v>46262.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46259.11458333334</v>
+        <v>46262.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46259.125</v>
+        <v>46262.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46259.13541666666</v>
+        <v>46262.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46259.14583333334</v>
+        <v>46262.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46259.15625</v>
+        <v>46262.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46259.16666666666</v>
+        <v>46262.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46259.17708333334</v>
+        <v>46262.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46259.1875</v>
+        <v>46262.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46259.19791666666</v>
+        <v>46262.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46259.20833333334</v>
+        <v>46262.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46259.21875</v>
+        <v>46262.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46259.22916666666</v>
+        <v>46262.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,58 +578,218 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46259.23958333334</v>
+        <v>46262.23958333334</v>
       </c>
       <c r="B25">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46259.25</v>
+        <v>46262.25</v>
       </c>
       <c r="B26">
-        <v>115</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46259.26041666666</v>
+        <v>46262.26041666666</v>
       </c>
       <c r="B27">
-        <v>235</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46259.27083333334</v>
+        <v>46262.27083333334</v>
       </c>
       <c r="B28">
-        <v>397</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46259.28125</v>
+        <v>46262.28125</v>
       </c>
       <c r="B29">
-        <v>576</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46259.29166666666</v>
+        <v>46262.29166666666</v>
       </c>
       <c r="B30">
-        <v>780</v>
+        <v>662</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46259.30208333334</v>
+        <v>46262.30208333334</v>
       </c>
       <c r="B31">
-        <v>1040</v>
+        <v>932</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2">
+        <v>46262.3125</v>
+      </c>
+      <c r="B32">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2">
+        <v>46262.32291666666</v>
+      </c>
+      <c r="B33">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2">
+        <v>46262.33333333334</v>
+      </c>
+      <c r="B34">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2">
+        <v>46262.34375</v>
+      </c>
+      <c r="B35">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2">
+        <v>46262.35416666666</v>
+      </c>
+      <c r="B36">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2">
+        <v>46262.36458333334</v>
+      </c>
+      <c r="B37">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2">
+        <v>46262.375</v>
+      </c>
+      <c r="B38">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2">
+        <v>46262.38541666666</v>
+      </c>
+      <c r="B39">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2">
+        <v>46262.39583333334</v>
+      </c>
+      <c r="B40">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2">
+        <v>46262.40625</v>
+      </c>
+      <c r="B41">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2">
+        <v>46262.41666666666</v>
+      </c>
+      <c r="B42">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2">
+        <v>46262.42708333334</v>
+      </c>
+      <c r="B43">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2">
+        <v>46262.4375</v>
+      </c>
+      <c r="B44">
+        <v>2763</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2">
+        <v>46262.44791666666</v>
+      </c>
+      <c r="B45">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2">
+        <v>46262.45833333334</v>
+      </c>
+      <c r="B46">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2">
+        <v>46262.46875</v>
+      </c>
+      <c r="B47">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2">
+        <v>46262.47916666666</v>
+      </c>
+      <c r="B48">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2">
+        <v>46262.48958333334</v>
+      </c>
+      <c r="B49">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2">
+        <v>46262.5</v>
+      </c>
+      <c r="B50">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2">
+        <v>46262.51041666666</v>
+      </c>
+      <c r="B51">
+        <v>3052</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Actual_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Actual_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46262.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46262.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46262.03125</v>
+        <v>46269.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46262.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46262.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46262.0625</v>
+        <v>46269.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46262.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46262.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46262.09375</v>
+        <v>46269.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46262.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46262.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46262.125</v>
+        <v>46269.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46262.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46262.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46262.15625</v>
+        <v>46269.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46262.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46262.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46262.1875</v>
+        <v>46269.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46262.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46262.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46262.21875</v>
+        <v>46269.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46262.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -578,218 +578,186 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46262.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46262.25</v>
+        <v>46269.25</v>
       </c>
       <c r="B26">
-        <v>87</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46262.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
       <c r="B27">
-        <v>166</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46262.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
       <c r="B28">
-        <v>285</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46262.28125</v>
+        <v>46269.28125</v>
       </c>
       <c r="B29">
-        <v>446</v>
+        <v>335</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46262.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
       <c r="B30">
-        <v>662</v>
+        <v>532</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46262.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
       <c r="B31">
-        <v>932</v>
+        <v>752</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46262.3125</v>
+        <v>46269.3125</v>
       </c>
       <c r="B32">
-        <v>1087</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46262.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
       <c r="B33">
-        <v>1227</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46262.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
       <c r="B34">
-        <v>1470</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46262.34375</v>
+        <v>46269.34375</v>
       </c>
       <c r="B35">
-        <v>1629</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46262.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
       <c r="B36">
-        <v>1794</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46262.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
       <c r="B37">
-        <v>2077</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46262.375</v>
+        <v>46269.375</v>
       </c>
       <c r="B38">
-        <v>2221</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46262.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="B39">
-        <v>2321</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46262.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
       <c r="B40">
-        <v>2442</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46262.40625</v>
+        <v>46269.40625</v>
       </c>
       <c r="B41">
-        <v>2519</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46262.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
       <c r="B42">
-        <v>2639</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46262.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
       <c r="B43">
-        <v>2703</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46262.4375</v>
+        <v>46269.4375</v>
       </c>
       <c r="B44">
-        <v>2763</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46262.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
       <c r="B45">
-        <v>2832</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46262.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
       <c r="B46">
-        <v>2872</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46262.46875</v>
+        <v>46269.46875</v>
       </c>
       <c r="B47">
-        <v>2941</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2">
-        <v>46262.47916666666</v>
-      </c>
-      <c r="B48">
-        <v>2932</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2">
-        <v>46262.48958333334</v>
-      </c>
-      <c r="B49">
-        <v>2994</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2">
-        <v>46262.5</v>
-      </c>
-      <c r="B50">
-        <v>2979</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2">
-        <v>46262.51041666666</v>
-      </c>
-      <c r="B51">
-        <v>3052</v>
+        <v>3038</v>
       </c>
     </row>
   </sheetData>
